--- a/stocks_metrics.xlsx
+++ b/stocks_metrics.xlsx
@@ -2,31 +2,23 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
   <sheets>
     <sheet name="Metrics" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
-      <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,25 +30,19 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -129,7 +115,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -171,72 +157,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -244,55 +172,15 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
-        </a:gradFill>
+        <a:solidFill>
+          <a:schemeClr val="dk1"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="accent1"/>
+        </a:solidFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
@@ -301,13 +189,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -341,24 +229,13 @@
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -384,7 +261,7 @@
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -406,8 +283,6 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -417,7 +292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P301"/>
+  <dimension ref="A1:U301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,6 +376,31 @@
           <t>Fetched_At</t>
         </is>
       </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>on_TradeRepublic</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>tr_matched_name</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>tr_match_confidence</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>tr_matched_query</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>tr_matched_isin</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -555,7 +455,28 @@
         <v>1.28814</v>
       </c>
       <c r="P2" s="1" t="n">
-        <v>46141.5667595519</v>
+        <v>46141.56675954861</v>
+      </c>
+      <c r="Q2" t="b">
+        <v>1</v>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
+        <v>100</v>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>US67066G1040</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -611,7 +532,28 @@
         <v>2.27273</v>
       </c>
       <c r="P3" s="1" t="n">
-        <v>46141.56677985535</v>
+        <v>46141.56677986111</v>
+      </c>
+      <c r="Q3" t="b">
+        <v>1</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Nokia</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
+        <v>100</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Nokia</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>FI0009000681</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -648,7 +590,6 @@
       <c r="I4" t="n">
         <v>424797503488</v>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
         <v>-0.05904</v>
       </c>
@@ -658,12 +599,32 @@
       <c r="M4" t="n">
         <v>36.028</v>
       </c>
-      <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
         <v>2.65957</v>
       </c>
       <c r="P4" s="1" t="n">
-        <v>46141.56679974655</v>
+        <v>46141.56679974537</v>
+      </c>
+      <c r="Q4" t="b">
+        <v>1</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
+        <v>100</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>US4581401001</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -700,7 +661,6 @@
       <c r="I5" t="n">
         <v>1226270720</v>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
         <v>0</v>
       </c>
@@ -710,10 +670,29 @@
       <c r="M5" t="n">
         <v>3.845</v>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
       <c r="P5" s="1" t="n">
-        <v>46141.56681923686</v>
+        <v>46141.56681923611</v>
+      </c>
+      <c r="Q5" t="b">
+        <v>1</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>POET Technologies</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
+        <v>100</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>POET Technologies</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>CA73044W3021</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -762,12 +741,32 @@
       <c r="M6" t="n">
         <v>18.487</v>
       </c>
-      <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
         <v>2.70833</v>
       </c>
       <c r="P6" s="1" t="n">
-        <v>46141.56683899595</v>
+        <v>46141.56683899306</v>
+      </c>
+      <c r="Q6" t="b">
+        <v>1</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>SoFi Technologies</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
+        <v>100</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>SoFi Technologies</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>US83406F1021</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -804,7 +803,6 @@
       <c r="I7" t="n">
         <v>1961353088</v>
       </c>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
         <v>-2.3021002</v>
       </c>
@@ -814,10 +812,29 @@
       <c r="M7" t="n">
         <v>18.764</v>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
       <c r="P7" s="1" t="n">
-        <v>46141.56685721152</v>
+        <v>46141.56685721065</v>
+      </c>
+      <c r="Q7" t="b">
+        <v>1</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>BigBear.ai</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>100</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>BigBear.ai</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>US08975B1098</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -873,7 +890,28 @@
         <v>2.44828</v>
       </c>
       <c r="P8" s="1" t="n">
-        <v>46141.56687705333</v>
+        <v>46141.56687704861</v>
+      </c>
+      <c r="Q8" t="b">
+        <v>1</v>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Pfizer</t>
+        </is>
+      </c>
+      <c r="S8" t="n">
+        <v>100</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Pfizer</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>US7170811035</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -910,20 +948,38 @@
       <c r="I9" t="n">
         <v>3076915456</v>
       </c>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
         <v>0</v>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>14.497</v>
       </c>
-      <c r="N9" t="inlineStr"/>
       <c r="O9" t="n">
         <v>1.7</v>
       </c>
       <c r="P9" s="1" t="n">
-        <v>46141.56689573564</v>
+        <v>46141.56689574074</v>
+      </c>
+      <c r="Q9" t="b">
+        <v>0</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Eramet</t>
+        </is>
+      </c>
+      <c r="S9" t="n">
+        <v>35</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>ERAS</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>FR0000131757</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -972,12 +1028,32 @@
       <c r="M10" t="n">
         <v>18.738</v>
       </c>
-      <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
         <v>2.34043</v>
       </c>
       <c r="P10" s="1" t="n">
-        <v>46141.56691485802</v>
+        <v>46141.56691486111</v>
+      </c>
+      <c r="Q10" t="b">
+        <v>1</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Tesla</t>
+        </is>
+      </c>
+      <c r="S10" t="n">
+        <v>100</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>US88160R1014</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -1026,12 +1102,32 @@
       <c r="M11" t="n">
         <v>23.576</v>
       </c>
-      <c r="N11" t="inlineStr"/>
       <c r="O11" t="n">
         <v>1.33333</v>
       </c>
       <c r="P11" s="1" t="n">
-        <v>46141.56693435389</v>
+        <v>46141.56693435185</v>
+      </c>
+      <c r="Q11" t="b">
+        <v>1</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Grab Holdings</t>
+        </is>
+      </c>
+      <c r="S11" t="n">
+        <v>100</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Grab</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>KYG4124C1096</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -1068,7 +1164,6 @@
       <c r="I12" t="n">
         <v>8779702272</v>
       </c>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="n">
         <v>0</v>
       </c>
@@ -1078,12 +1173,32 @@
       <c r="M12" t="n">
         <v>3.14</v>
       </c>
-      <c r="N12" t="inlineStr"/>
       <c r="O12" t="n">
         <v>3</v>
       </c>
       <c r="P12" s="1" t="n">
-        <v>46141.56695372065</v>
+        <v>46141.56695371528</v>
+      </c>
+      <c r="Q12" t="b">
+        <v>1</v>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Joby Aviation Inc. Registered Shares DL -,0001</t>
+        </is>
+      </c>
+      <c r="S12" t="n">
+        <v>100</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Joby Aviation</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>KYG651631007</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -1120,7 +1235,6 @@
       <c r="I13" t="n">
         <v>5073196544</v>
       </c>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="n">
         <v>-2.60233</v>
       </c>
@@ -1130,12 +1244,32 @@
       <c r="M13" t="n">
         <v>5.345</v>
       </c>
-      <c r="N13" t="inlineStr"/>
       <c r="O13" t="n">
         <v>1.25</v>
       </c>
       <c r="P13" s="1" t="n">
-        <v>46141.56697206127</v>
+        <v>46141.56697206019</v>
+      </c>
+      <c r="Q13" t="b">
+        <v>1</v>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Ondas Holdings</t>
+        </is>
+      </c>
+      <c r="S13" t="n">
+        <v>100</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Ondas</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>US68236H2040</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -1184,12 +1318,32 @@
       <c r="M14" t="n">
         <v>2.065</v>
       </c>
-      <c r="N14" t="inlineStr"/>
       <c r="O14" t="n">
         <v>1</v>
       </c>
       <c r="P14" s="1" t="n">
-        <v>46141.56699110733</v>
+        <v>46141.56699111111</v>
+      </c>
+      <c r="Q14" t="b">
+        <v>1</v>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Kopin</t>
+        </is>
+      </c>
+      <c r="S14" t="n">
+        <v>100</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kopin</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>US5006001011</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -1226,7 +1380,6 @@
       <c r="I15" t="n">
         <v>49737416704</v>
       </c>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="n">
         <v>-0.04369</v>
       </c>
@@ -1243,7 +1396,28 @@
         <v>2.68182</v>
       </c>
       <c r="P15" s="1" t="n">
-        <v>46141.56701182856</v>
+        <v>46141.5670118287</v>
+      </c>
+      <c r="Q15" t="b">
+        <v>1</v>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Ford Motor</t>
+        </is>
+      </c>
+      <c r="S15" t="n">
+        <v>100</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Ford Motor</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>US3453708600</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -1289,13 +1463,32 @@
       <c r="L16" t="n">
         <v>0.108</v>
       </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="O16" t="n">
         <v>2.15385</v>
       </c>
       <c r="P16" s="1" t="n">
-        <v>46141.56703107223</v>
+        <v>46141.56703107639</v>
+      </c>
+      <c r="Q16" t="b">
+        <v>1</v>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>American Airlines</t>
+        </is>
+      </c>
+      <c r="S16" t="n">
+        <v>100</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>American Airlines</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>US02376R1023</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -1351,7 +1544,28 @@
         <v>1.45238</v>
       </c>
       <c r="P17" s="1" t="n">
-        <v>46141.5670504977</v>
+        <v>46141.56705049769</v>
+      </c>
+      <c r="Q17" t="b">
+        <v>1</v>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Micron Technology</t>
+        </is>
+      </c>
+      <c r="S17" t="n">
+        <v>100</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Micron Technology</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>US5951121038</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -1400,12 +1614,32 @@
       <c r="M18" t="n">
         <v>6.359</v>
       </c>
-      <c r="N18" t="inlineStr"/>
       <c r="O18" t="n">
         <v>1.57143</v>
       </c>
       <c r="P18" s="1" t="n">
-        <v>46141.56707143746</v>
+        <v>46141.56707143519</v>
+      </c>
+      <c r="Q18" t="b">
+        <v>1</v>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="S18" t="n">
+        <v>100</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>US0079031078</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1442,7 +1676,6 @@
       <c r="I19" t="n">
         <v>4223683840</v>
       </c>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="n">
         <v>-2.29828</v>
       </c>
@@ -1452,12 +1685,32 @@
       <c r="M19" t="n">
         <v>99.38800000000001</v>
       </c>
-      <c r="N19" t="inlineStr"/>
       <c r="O19" t="n">
         <v>2.8</v>
       </c>
       <c r="P19" s="1" t="n">
-        <v>46141.56709021412</v>
+        <v>46141.56709021991</v>
+      </c>
+      <c r="Q19" t="b">
+        <v>1</v>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Plug Power</t>
+        </is>
+      </c>
+      <c r="S19" t="n">
+        <v>100</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Plug Power</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>US72919P2020</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -1494,7 +1747,6 @@
       <c r="I20" t="n">
         <v>3489586688</v>
       </c>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="n">
         <v>-2.54711</v>
       </c>
@@ -1504,12 +1756,32 @@
       <c r="M20" t="n">
         <v>1.459</v>
       </c>
-      <c r="N20" t="inlineStr"/>
       <c r="O20" t="n">
         <v>2.875</v>
       </c>
       <c r="P20" s="1" t="n">
-        <v>46141.56711011647</v>
+        <v>46141.56711011574</v>
+      </c>
+      <c r="Q20" t="b">
+        <v>1</v>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Navitas Semiconductor Corp. Reg. Shares Cl.A DL-,0001</t>
+        </is>
+      </c>
+      <c r="S20" t="n">
+        <v>100</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Navitas Semiconductor</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>US63942X1063</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -1558,12 +1830,32 @@
       <c r="M21" t="n">
         <v>43.435</v>
       </c>
-      <c r="N21" t="inlineStr"/>
       <c r="O21" t="n">
         <v>1.35821</v>
       </c>
       <c r="P21" s="1" t="n">
-        <v>46141.5671291353</v>
+        <v>46141.56712913194</v>
+      </c>
+      <c r="Q21" t="b">
+        <v>1</v>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Amazon.com</t>
+        </is>
+      </c>
+      <c r="S21" t="n">
+        <v>100</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Amazon.com</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>US0231351067</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -1612,12 +1904,14 @@
       <c r="M22" t="n">
         <v>153.017</v>
       </c>
-      <c r="N22" t="inlineStr"/>
       <c r="O22" t="n">
         <v>1.875</v>
       </c>
       <c r="P22" s="1" t="n">
-        <v>46141.56714830981</v>
+        <v>46141.56714831018</v>
+      </c>
+      <c r="Q22" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1654,7 +1948,6 @@
       <c r="I23" t="n">
         <v>5251623936</v>
       </c>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="n">
         <v>-0.29740998</v>
       </c>
@@ -1664,12 +1957,14 @@
       <c r="M23" t="n">
         <v>131.343</v>
       </c>
-      <c r="N23" t="inlineStr"/>
       <c r="O23" t="n">
         <v>3.25</v>
       </c>
       <c r="P23" s="1" t="n">
-        <v>46141.5671684655</v>
+        <v>46141.56716846065</v>
+      </c>
+      <c r="Q23" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1706,7 +2001,6 @@
       <c r="I24" t="n">
         <v>7514836480</v>
       </c>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="n">
         <v>-0.73517996</v>
       </c>
@@ -1716,12 +2010,14 @@
       <c r="M24" t="n">
         <v>73.643</v>
       </c>
-      <c r="N24" t="inlineStr"/>
       <c r="O24" t="n">
         <v>3</v>
       </c>
       <c r="P24" s="1" t="n">
-        <v>46141.56718754584</v>
+        <v>46141.56718754629</v>
+      </c>
+      <c r="Q24" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1777,7 +2073,10 @@
         <v>3.375</v>
       </c>
       <c r="P25" s="1" t="n">
-        <v>46141.56720659164</v>
+        <v>46141.56720659722</v>
+      </c>
+      <c r="Q25" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1814,7 +2113,6 @@
       <c r="I26" t="n">
         <v>1568229760</v>
       </c>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="n">
         <v>0</v>
       </c>
@@ -1824,10 +2122,11 @@
       <c r="M26" t="n">
         <v>1.651</v>
       </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
       <c r="P26" s="1" t="n">
-        <v>46141.56722703834</v>
+        <v>46141.56722703703</v>
+      </c>
+      <c r="Q26" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1883,7 +2182,10 @@
         <v>1.63636</v>
       </c>
       <c r="P27" s="1" t="n">
-        <v>46141.56724663493</v>
+        <v>46141.56724663194</v>
+      </c>
+      <c r="Q27" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -1920,7 +2222,6 @@
       <c r="I28" t="n">
         <v>15936043008</v>
       </c>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="n">
         <v>-0.17798</v>
       </c>
@@ -1930,12 +2231,14 @@
       <c r="M28" t="n">
         <v>246.311</v>
       </c>
-      <c r="N28" t="inlineStr"/>
       <c r="O28" t="n">
         <v>2.04</v>
       </c>
       <c r="P28" s="1" t="n">
-        <v>46141.56727150964</v>
+        <v>46141.56727150463</v>
+      </c>
+      <c r="Q28" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -1972,7 +2275,6 @@
       <c r="I29" t="n">
         <v>10049263616</v>
       </c>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="n">
         <v>-0.07764</v>
       </c>
@@ -1982,12 +2284,14 @@
       <c r="M29" t="n">
         <v>181.597</v>
       </c>
-      <c r="N29" t="inlineStr"/>
       <c r="O29" t="n">
         <v>2.69767</v>
       </c>
       <c r="P29" s="1" t="n">
-        <v>46141.56729125961</v>
+        <v>46141.56729126158</v>
+      </c>
+      <c r="Q29" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2024,7 +2328,6 @@
       <c r="I30" t="n">
         <v>4190185728</v>
       </c>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="n">
         <v>-1.44581</v>
       </c>
@@ -2034,12 +2337,14 @@
       <c r="M30" t="n">
         <v>104.839</v>
       </c>
-      <c r="N30" t="inlineStr"/>
       <c r="O30" t="n">
         <v>2.28571</v>
       </c>
       <c r="P30" s="1" t="n">
-        <v>46141.56730982052</v>
+        <v>46141.56730981482</v>
+      </c>
+      <c r="Q30" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2088,12 +2393,14 @@
       <c r="M31" t="n">
         <v>53.788</v>
       </c>
-      <c r="N31" t="inlineStr"/>
       <c r="O31" t="n">
         <v>1.7</v>
       </c>
       <c r="P31" s="1" t="n">
-        <v>46141.56733195262</v>
+        <v>46141.56733195602</v>
+      </c>
+      <c r="Q31" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2130,7 +2437,6 @@
       <c r="I32" t="n">
         <v>12234510336</v>
       </c>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="n">
         <v>0</v>
       </c>
@@ -2147,7 +2453,10 @@
         <v>1</v>
       </c>
       <c r="P32" s="1" t="n">
-        <v>46141.56734951236</v>
+        <v>46141.56734951389</v>
+      </c>
+      <c r="Q32" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2203,7 +2512,10 @@
         <v>2</v>
       </c>
       <c r="P33" s="1" t="n">
-        <v>46141.56736940118</v>
+        <v>46141.56736939815</v>
+      </c>
+      <c r="Q33" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2259,7 +2571,10 @@
         <v>1.89362</v>
       </c>
       <c r="P34" s="1" t="n">
-        <v>46141.56738827554</v>
+        <v>46141.56738827546</v>
+      </c>
+      <c r="Q34" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2296,7 +2611,6 @@
       <c r="I35" t="n">
         <v>55740956672</v>
       </c>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="n">
         <v>-0.22744</v>
       </c>
@@ -2306,12 +2620,14 @@
       <c r="M35" t="n">
         <v>894.2430000000001</v>
       </c>
-      <c r="N35" t="inlineStr"/>
       <c r="O35" t="n">
         <v>1.85294</v>
       </c>
       <c r="P35" s="1" t="n">
-        <v>46141.56740597639</v>
+        <v>46141.56740597222</v>
+      </c>
+      <c r="Q35" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2367,7 +2683,10 @@
         <v>1.70833</v>
       </c>
       <c r="P36" s="1" t="n">
-        <v>46141.56742631964</v>
+        <v>46141.56742631945</v>
+      </c>
+      <c r="Q36" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2423,7 +2742,10 @@
         <v>1.2766</v>
       </c>
       <c r="P37" s="1" t="n">
-        <v>46141.56744664083</v>
+        <v>46141.56744664352</v>
+      </c>
+      <c r="Q37" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2479,7 +2801,10 @@
         <v>1.28571</v>
       </c>
       <c r="P38" s="1" t="n">
-        <v>46141.56746601591</v>
+        <v>46141.56746601852</v>
+      </c>
+      <c r="Q38" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2535,7 +2860,10 @@
         <v>1.92</v>
       </c>
       <c r="P39" s="1" t="n">
-        <v>46141.5674869986</v>
+        <v>46141.56748700231</v>
+      </c>
+      <c r="Q39" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2572,7 +2900,6 @@
       <c r="I40" t="n">
         <v>10189752320</v>
       </c>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="n">
         <v>0</v>
       </c>
@@ -2582,12 +2909,14 @@
       <c r="M40" t="n">
         <v>3699.474</v>
       </c>
-      <c r="N40" t="inlineStr"/>
       <c r="O40" t="n">
         <v>1.38462</v>
       </c>
       <c r="P40" s="1" t="n">
-        <v>46141.56750661114</v>
+        <v>46141.56750660879</v>
+      </c>
+      <c r="Q40" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2643,7 +2972,10 @@
         <v>1.52381</v>
       </c>
       <c r="P41" s="1" t="n">
-        <v>46141.5675265442</v>
+        <v>46141.56752653935</v>
+      </c>
+      <c r="Q41" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2680,20 +3012,20 @@
       <c r="I42" t="n">
         <v>3826537216</v>
       </c>
-      <c r="J42" t="inlineStr"/>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
         <v>-0.947</v>
       </c>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="O42" t="n">
         <v>2.52941</v>
       </c>
       <c r="P42" s="1" t="n">
-        <v>46141.56754627718</v>
+        <v>46141.56754627315</v>
+      </c>
+      <c r="Q42" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2730,7 +3062,6 @@
       <c r="I43" t="n">
         <v>1742239872</v>
       </c>
-      <c r="J43" t="inlineStr"/>
       <c r="K43" t="n">
         <v>-1.24105</v>
       </c>
@@ -2740,10 +3071,11 @@
       <c r="M43" t="n">
         <v>122.022</v>
       </c>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
       <c r="P43" s="1" t="n">
-        <v>46141.56756509968</v>
+        <v>46141.56756510417</v>
+      </c>
+      <c r="Q43" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2780,11 +3112,9 @@
       <c r="I44" t="n">
         <v>3662052352</v>
       </c>
-      <c r="J44" t="inlineStr"/>
       <c r="K44" t="n">
         <v>-0.40772998</v>
       </c>
-      <c r="L44" t="inlineStr"/>
       <c r="M44" t="n">
         <v>4.939</v>
       </c>
@@ -2795,7 +3125,10 @@
         <v>2.27273</v>
       </c>
       <c r="P44" s="1" t="n">
-        <v>46141.56758412433</v>
+        <v>46141.56758412037</v>
+      </c>
+      <c r="Q44" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2851,7 +3184,10 @@
         <v>2.74074</v>
       </c>
       <c r="P45" s="1" t="n">
-        <v>46141.56760509322</v>
+        <v>46141.56760509259</v>
+      </c>
+      <c r="Q45" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -2897,7 +3233,6 @@
       <c r="L46" t="n">
         <v>0.06</v>
       </c>
-      <c r="M46" t="inlineStr"/>
       <c r="N46" t="n">
         <v>5.54</v>
       </c>
@@ -2905,7 +3240,10 @@
         <v>2</v>
       </c>
       <c r="P46" s="1" t="n">
-        <v>46141.56762455621</v>
+        <v>46141.56762456019</v>
+      </c>
+      <c r="Q46" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -2942,7 +3280,6 @@
       <c r="I47" t="n">
         <v>5829638144</v>
       </c>
-      <c r="J47" t="inlineStr"/>
       <c r="K47" t="n">
         <v>-0.064380005</v>
       </c>
@@ -2952,12 +3289,14 @@
       <c r="M47" t="n">
         <v>129.324</v>
       </c>
-      <c r="N47" t="inlineStr"/>
       <c r="O47" t="n">
         <v>2.83333</v>
       </c>
       <c r="P47" s="1" t="n">
-        <v>46141.56764410775</v>
+        <v>46141.5676441088</v>
+      </c>
+      <c r="Q47" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3013,7 +3352,10 @@
         <v>1.86667</v>
       </c>
       <c r="P48" s="1" t="n">
-        <v>46141.56766362382</v>
+        <v>46141.56766362269</v>
+      </c>
+      <c r="Q48" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3050,7 +3392,6 @@
       <c r="I49" t="n">
         <v>9176059904</v>
       </c>
-      <c r="J49" t="inlineStr"/>
       <c r="K49" t="n">
         <v>-0.59472</v>
       </c>
@@ -3060,12 +3401,14 @@
       <c r="M49" t="n">
         <v>110.128</v>
       </c>
-      <c r="N49" t="inlineStr"/>
       <c r="O49" t="n">
         <v>1.18182</v>
       </c>
       <c r="P49" s="1" t="n">
-        <v>46141.56768230416</v>
+        <v>46141.56768230324</v>
+      </c>
+      <c r="Q49" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3121,7 +3464,10 @@
         <v>1.48837</v>
       </c>
       <c r="P50" s="1" t="n">
-        <v>46141.56770163413</v>
+        <v>46141.56770163195</v>
+      </c>
+      <c r="Q50" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3170,12 +3516,14 @@
       <c r="M51" t="n">
         <v>3.063</v>
       </c>
-      <c r="N51" t="inlineStr"/>
       <c r="O51" t="n">
         <v>1.93333</v>
       </c>
       <c r="P51" s="1" t="n">
-        <v>46141.56772120931</v>
+        <v>46141.5677212037</v>
+      </c>
+      <c r="Q51" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3231,7 +3579,10 @@
         <v>1.39394</v>
       </c>
       <c r="P52" s="1" t="n">
-        <v>46141.56774054023</v>
+        <v>46141.56774054398</v>
+      </c>
+      <c r="Q52" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3277,13 +3628,14 @@
       <c r="L53" t="n">
         <v>0.439</v>
       </c>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="O53" t="n">
         <v>1.38095</v>
       </c>
       <c r="P53" s="1" t="n">
-        <v>46141.56775940044</v>
+        <v>46141.56775939815</v>
+      </c>
+      <c r="Q53" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3332,12 +3684,14 @@
       <c r="M54" t="n">
         <v>207.161</v>
       </c>
-      <c r="N54" t="inlineStr"/>
       <c r="O54" t="n">
         <v>2.75</v>
       </c>
       <c r="P54" s="1" t="n">
-        <v>46141.56777828903</v>
+        <v>46141.56777828703</v>
+      </c>
+      <c r="Q54" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3374,7 +3728,6 @@
       <c r="I55" t="n">
         <v>7006057984</v>
       </c>
-      <c r="J55" t="inlineStr"/>
       <c r="K55" t="n">
         <v>0</v>
       </c>
@@ -3384,12 +3737,14 @@
       <c r="M55" t="n">
         <v>331.044</v>
       </c>
-      <c r="N55" t="inlineStr"/>
       <c r="O55" t="n">
         <v>1.35714</v>
       </c>
       <c r="P55" s="1" t="n">
-        <v>46141.56779782056</v>
+        <v>46141.56779782407</v>
+      </c>
+      <c r="Q55" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3426,20 +3781,20 @@
       <c r="I56" t="n">
         <v>4287561216</v>
       </c>
-      <c r="J56" t="inlineStr"/>
       <c r="K56" t="n">
         <v>0</v>
       </c>
-      <c r="L56" t="inlineStr"/>
       <c r="M56" t="n">
         <v>6.235</v>
       </c>
-      <c r="N56" t="inlineStr"/>
       <c r="O56" t="n">
         <v>3.44444</v>
       </c>
       <c r="P56" s="1" t="n">
-        <v>46141.56781688442</v>
+        <v>46141.56781688657</v>
+      </c>
+      <c r="Q56" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3488,12 +3843,14 @@
       <c r="M57" t="n">
         <v>179.319</v>
       </c>
-      <c r="N57" t="inlineStr"/>
       <c r="O57" t="n">
         <v>1.73684</v>
       </c>
       <c r="P57" s="1" t="n">
-        <v>46141.56783746935</v>
+        <v>46141.56783746528</v>
+      </c>
+      <c r="Q57" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3539,7 +3896,6 @@
       <c r="L58" t="n">
         <v>0.11</v>
       </c>
-      <c r="M58" t="inlineStr"/>
       <c r="N58" t="n">
         <v>1.19</v>
       </c>
@@ -3547,7 +3903,10 @@
         <v>1.875</v>
       </c>
       <c r="P58" s="1" t="n">
-        <v>46141.56785688594</v>
+        <v>46141.56785688658</v>
+      </c>
+      <c r="Q58" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3584,7 +3943,6 @@
       <c r="I59" t="n">
         <v>1071177408</v>
       </c>
-      <c r="J59" t="inlineStr"/>
       <c r="K59" t="n">
         <v>-0.00756</v>
       </c>
@@ -3594,12 +3952,14 @@
       <c r="M59" t="n">
         <v>114.554</v>
       </c>
-      <c r="N59" t="inlineStr"/>
       <c r="O59" t="n">
         <v>2.2</v>
       </c>
       <c r="P59" s="1" t="n">
-        <v>46141.5678751476</v>
+        <v>46141.56787515046</v>
+      </c>
+      <c r="Q59" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3655,7 +4015,10 @@
         <v>1.61111</v>
       </c>
       <c r="P60" s="1" t="n">
-        <v>46141.56789548831</v>
+        <v>46141.56789548611</v>
+      </c>
+      <c r="Q60" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3704,12 +4067,14 @@
       <c r="M61" t="n">
         <v>3.901</v>
       </c>
-      <c r="N61" t="inlineStr"/>
       <c r="O61" t="n">
         <v>2.78947</v>
       </c>
       <c r="P61" s="1" t="n">
-        <v>46141.56791469443</v>
+        <v>46141.56791469907</v>
+      </c>
+      <c r="Q61" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3758,12 +4123,14 @@
       <c r="M62" t="n">
         <v>136.04</v>
       </c>
-      <c r="N62" t="inlineStr"/>
       <c r="O62" t="n">
         <v>1.92593</v>
       </c>
       <c r="P62" s="1" t="n">
-        <v>46141.56793301347</v>
+        <v>46141.56793300926</v>
+      </c>
+      <c r="Q62" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -3812,12 +4179,14 @@
       <c r="M63" t="n">
         <v>75.28</v>
       </c>
-      <c r="N63" t="inlineStr"/>
       <c r="O63" t="n">
         <v>2.88889</v>
       </c>
       <c r="P63" s="1" t="n">
-        <v>46141.56795231538</v>
+        <v>46141.56795231481</v>
+      </c>
+      <c r="Q63" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -3854,7 +4223,6 @@
       <c r="I64" t="n">
         <v>1860094464</v>
       </c>
-      <c r="J64" t="inlineStr"/>
       <c r="K64" t="n">
         <v>-0.07782</v>
       </c>
@@ -3864,12 +4232,14 @@
       <c r="M64" t="n">
         <v>515.691</v>
       </c>
-      <c r="N64" t="inlineStr"/>
       <c r="O64" t="n">
         <v>3.35294</v>
       </c>
       <c r="P64" s="1" t="n">
-        <v>46141.56797213125</v>
+        <v>46141.56797212963</v>
+      </c>
+      <c r="Q64" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -3906,7 +4276,6 @@
       <c r="I65" t="n">
         <v>6282115072</v>
       </c>
-      <c r="J65" t="inlineStr"/>
       <c r="K65" t="n">
         <v>-1.02432</v>
       </c>
@@ -3916,12 +4285,14 @@
       <c r="M65" t="n">
         <v>30.323</v>
       </c>
-      <c r="N65" t="inlineStr"/>
       <c r="O65" t="n">
         <v>1.42105</v>
       </c>
       <c r="P65" s="1" t="n">
-        <v>46141.56799089219</v>
+        <v>46141.56799089121</v>
+      </c>
+      <c r="Q65" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -3958,7 +4329,6 @@
       <c r="I66" t="n">
         <v>14215837696</v>
       </c>
-      <c r="J66" t="inlineStr"/>
       <c r="K66" t="n">
         <v>-0.04083</v>
       </c>
@@ -3968,12 +4338,14 @@
       <c r="M66" t="n">
         <v>40.327</v>
       </c>
-      <c r="N66" t="inlineStr"/>
       <c r="O66" t="n">
         <v>1.2</v>
       </c>
       <c r="P66" s="1" t="n">
-        <v>46141.56800989305</v>
+        <v>46141.56800989583</v>
+      </c>
+      <c r="Q66" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4010,7 +4382,6 @@
       <c r="I67" t="n">
         <v>15794884608</v>
       </c>
-      <c r="J67" t="inlineStr"/>
       <c r="K67" t="n">
         <v>0</v>
       </c>
@@ -4020,12 +4391,14 @@
       <c r="M67" t="n">
         <v>0.787</v>
       </c>
-      <c r="N67" t="inlineStr"/>
       <c r="O67" t="n">
         <v>1.5</v>
       </c>
       <c r="P67" s="1" t="n">
-        <v>46141.56802817806</v>
+        <v>46141.56802818287</v>
+      </c>
+      <c r="Q67" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4081,7 +4454,10 @@
         <v>1.875</v>
       </c>
       <c r="P68" s="1" t="n">
-        <v>46141.56804828504</v>
+        <v>46141.56804828704</v>
+      </c>
+      <c r="Q68" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4137,7 +4513,10 @@
         <v>2.24</v>
       </c>
       <c r="P69" s="1" t="n">
-        <v>46141.56806846437</v>
+        <v>46141.56806846065</v>
+      </c>
+      <c r="Q69" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4193,7 +4572,10 @@
         <v>2.16</v>
       </c>
       <c r="P70" s="1" t="n">
-        <v>46141.56809023675</v>
+        <v>46141.56809023148</v>
+      </c>
+      <c r="Q70" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -4249,7 +4631,10 @@
         <v>2.23529</v>
       </c>
       <c r="P71" s="1" t="n">
-        <v>46141.56811215398</v>
+        <v>46141.56811215278</v>
+      </c>
+      <c r="Q71" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4286,7 +4671,6 @@
       <c r="I72" t="n">
         <v>1546676224</v>
       </c>
-      <c r="J72" t="inlineStr"/>
       <c r="K72" t="n">
         <v>-0.11054</v>
       </c>
@@ -4296,12 +4680,14 @@
       <c r="M72" t="n">
         <v>0.173</v>
       </c>
-      <c r="N72" t="inlineStr"/>
       <c r="O72" t="n">
         <v>1</v>
       </c>
       <c r="P72" s="1" t="n">
-        <v>46141.56813918165</v>
+        <v>46141.56813917824</v>
+      </c>
+      <c r="Q72" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -4338,7 +4724,6 @@
       <c r="I73" t="n">
         <v>3435253248</v>
       </c>
-      <c r="J73" t="inlineStr"/>
       <c r="K73" t="n">
         <v>-0.08291</v>
       </c>
@@ -4348,12 +4733,14 @@
       <c r="M73" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="N73" t="inlineStr"/>
       <c r="O73" t="n">
         <v>1.5</v>
       </c>
       <c r="P73" s="1" t="n">
-        <v>46141.56816030308</v>
+        <v>46141.56816030093</v>
+      </c>
+      <c r="Q73" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -4402,12 +4789,14 @@
       <c r="M74" t="n">
         <v>20.728</v>
       </c>
-      <c r="N74" t="inlineStr"/>
       <c r="O74" t="n">
         <v>1.4375</v>
       </c>
       <c r="P74" s="1" t="n">
-        <v>46141.56818101443</v>
+        <v>46141.56818101852</v>
+      </c>
+      <c r="Q74" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -4456,12 +4845,14 @@
       <c r="M75" t="n">
         <v>100.26</v>
       </c>
-      <c r="N75" t="inlineStr"/>
       <c r="O75" t="n">
         <v>1.64706</v>
       </c>
       <c r="P75" s="1" t="n">
-        <v>46141.56820291758</v>
+        <v>46141.56820291666</v>
+      </c>
+      <c r="Q75" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -4504,16 +4895,17 @@
       <c r="K76" t="n">
         <v>1.18228</v>
       </c>
-      <c r="L76" t="inlineStr"/>
       <c r="M76" t="n">
         <v>2669.192</v>
       </c>
-      <c r="N76" t="inlineStr"/>
       <c r="O76" t="n">
         <v>2.2</v>
       </c>
       <c r="P76" s="1" t="n">
-        <v>46141.56822355663</v>
+        <v>46141.56822355324</v>
+      </c>
+      <c r="Q76" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -4569,7 +4961,10 @@
         <v>2.69231</v>
       </c>
       <c r="P77" s="1" t="n">
-        <v>46141.56828096075</v>
+        <v>46141.56828096065</v>
+      </c>
+      <c r="Q77" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -4625,7 +5020,10 @@
         <v>2.72222</v>
       </c>
       <c r="P78" s="1" t="n">
-        <v>46141.56830237294</v>
+        <v>46141.56830237269</v>
+      </c>
+      <c r="Q78" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -4662,20 +5060,20 @@
       <c r="I79" t="n">
         <v>9702833152</v>
       </c>
-      <c r="J79" t="inlineStr"/>
       <c r="K79" t="n">
         <v>0</v>
       </c>
-      <c r="L79" t="inlineStr"/>
       <c r="M79" t="n">
         <v>3.925</v>
       </c>
-      <c r="N79" t="inlineStr"/>
       <c r="O79" t="n">
         <v>2.11111</v>
       </c>
       <c r="P79" s="1" t="n">
-        <v>46141.56832192509</v>
+        <v>46141.5683219213</v>
+      </c>
+      <c r="Q79" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -4724,12 +5122,14 @@
       <c r="M80" t="n">
         <v>10.835</v>
       </c>
-      <c r="N80" t="inlineStr"/>
       <c r="O80" t="n">
         <v>1.6</v>
       </c>
       <c r="P80" s="1" t="n">
-        <v>46141.56834152736</v>
+        <v>46141.56834152777</v>
+      </c>
+      <c r="Q80" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -4766,20 +5166,20 @@
       <c r="I81" t="n">
         <v>955787456</v>
       </c>
-      <c r="J81" t="inlineStr"/>
       <c r="K81" t="n">
         <v>-0.13042</v>
       </c>
       <c r="L81" t="n">
         <v>-0.014</v>
       </c>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
       <c r="O81" t="n">
         <v>3</v>
       </c>
       <c r="P81" s="1" t="n">
-        <v>46141.56836093149</v>
+        <v>46141.56836092593</v>
+      </c>
+      <c r="Q81" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="82">
@@ -4816,7 +5216,6 @@
       <c r="I82" t="n">
         <v>1755723648</v>
       </c>
-      <c r="J82" t="inlineStr"/>
       <c r="K82" t="n">
         <v>-0.5427</v>
       </c>
@@ -4826,12 +5225,14 @@
       <c r="M82" t="n">
         <v>579.84</v>
       </c>
-      <c r="N82" t="inlineStr"/>
       <c r="O82" t="n">
         <v>2.36364</v>
       </c>
       <c r="P82" s="1" t="n">
-        <v>46141.56838108031</v>
+        <v>46141.56838107639</v>
+      </c>
+      <c r="Q82" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -4868,20 +5269,20 @@
       <c r="I83" t="n">
         <v>4379207168</v>
       </c>
-      <c r="J83" t="inlineStr"/>
       <c r="K83" t="n">
         <v>0</v>
       </c>
-      <c r="L83" t="inlineStr"/>
       <c r="M83" t="n">
         <v>5.534</v>
       </c>
-      <c r="N83" t="inlineStr"/>
       <c r="O83" t="n">
         <v>1.88889</v>
       </c>
       <c r="P83" s="1" t="n">
-        <v>46141.56840073606</v>
+        <v>46141.56840074074</v>
+      </c>
+      <c r="Q83" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="84">
@@ -4937,7 +5338,10 @@
         <v>1.84615</v>
       </c>
       <c r="P84" s="1" t="n">
-        <v>46141.56842151869</v>
+        <v>46141.5684215162</v>
+      </c>
+      <c r="Q84" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="85">
@@ -4993,7 +5397,10 @@
         <v>1.46341</v>
       </c>
       <c r="P85" s="1" t="n">
-        <v>46141.56844261994</v>
+        <v>46141.56844261574</v>
+      </c>
+      <c r="Q85" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="86">
@@ -5049,7 +5456,10 @@
         <v>1.54545</v>
       </c>
       <c r="P86" s="1" t="n">
-        <v>46141.5684621578</v>
+        <v>46141.56846215278</v>
+      </c>
+      <c r="Q86" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="87">
@@ -5095,7 +5505,6 @@
       <c r="L87" t="n">
         <v>0.118</v>
       </c>
-      <c r="M87" t="inlineStr"/>
       <c r="N87" t="n">
         <v>2.13</v>
       </c>
@@ -5103,7 +5512,10 @@
         <v>1.48</v>
       </c>
       <c r="P87" s="1" t="n">
-        <v>46141.56848204348</v>
+        <v>46141.56848204861</v>
+      </c>
+      <c r="Q87" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="88">
@@ -5140,20 +5552,20 @@
       <c r="I88" t="n">
         <v>1709058432</v>
       </c>
-      <c r="J88" t="inlineStr"/>
       <c r="K88" t="n">
         <v>0</v>
       </c>
-      <c r="L88" t="inlineStr"/>
       <c r="M88" t="n">
         <v>33.763</v>
       </c>
-      <c r="N88" t="inlineStr"/>
       <c r="O88" t="n">
         <v>2.72727</v>
       </c>
       <c r="P88" s="1" t="n">
-        <v>46141.56850113353</v>
+        <v>46141.56850113426</v>
+      </c>
+      <c r="Q88" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="89">
@@ -5190,20 +5602,20 @@
       <c r="I89" t="n">
         <v>2312014080</v>
       </c>
-      <c r="J89" t="inlineStr"/>
       <c r="K89" t="n">
         <v>0</v>
       </c>
       <c r="L89" t="n">
         <v>6.996</v>
       </c>
-      <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
       <c r="O89" t="n">
         <v>2.55556</v>
       </c>
       <c r="P89" s="1" t="n">
-        <v>46141.56852161102</v>
+        <v>46141.56852160879</v>
+      </c>
+      <c r="Q89" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -5249,13 +5661,14 @@
       <c r="L90" t="n">
         <v>0.144</v>
       </c>
-      <c r="M90" t="inlineStr"/>
       <c r="N90" t="n">
         <v>3.75</v>
       </c>
-      <c r="O90" t="inlineStr"/>
       <c r="P90" s="1" t="n">
-        <v>46141.56854316818</v>
+        <v>46141.5685431713</v>
+      </c>
+      <c r="Q90" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="91">
@@ -5292,7 +5705,6 @@
       <c r="I91" t="n">
         <v>24477515776</v>
       </c>
-      <c r="J91" t="inlineStr"/>
       <c r="K91" t="n">
         <v>-0.0359</v>
       </c>
@@ -5302,12 +5714,14 @@
       <c r="M91" t="n">
         <v>76.04900000000001</v>
       </c>
-      <c r="N91" t="inlineStr"/>
       <c r="O91" t="n">
         <v>2.75</v>
       </c>
       <c r="P91" s="1" t="n">
-        <v>46141.56856193868</v>
+        <v>46141.56856194444</v>
+      </c>
+      <c r="Q91" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="92">
@@ -5363,7 +5777,10 @@
         <v>2.35714</v>
       </c>
       <c r="P92" s="1" t="n">
-        <v>46141.56858147521</v>
+        <v>46141.56858146991</v>
+      </c>
+      <c r="Q92" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="93">
@@ -5419,7 +5836,10 @@
         <v>2.78571</v>
       </c>
       <c r="P93" s="1" t="n">
-        <v>46141.56860156492</v>
+        <v>46141.5686015625</v>
+      </c>
+      <c r="Q93" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="94">
@@ -5456,7 +5876,6 @@
       <c r="I94" t="n">
         <v>582490560</v>
       </c>
-      <c r="J94" t="inlineStr"/>
       <c r="K94" t="n">
         <v>-0.48634</v>
       </c>
@@ -5466,10 +5885,11 @@
       <c r="M94" t="n">
         <v>3.233</v>
       </c>
-      <c r="N94" t="inlineStr"/>
-      <c r="O94" t="inlineStr"/>
       <c r="P94" s="1" t="n">
-        <v>46141.5686214047</v>
+        <v>46141.56862140046</v>
+      </c>
+      <c r="Q94" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="95">
@@ -5518,12 +5938,14 @@
       <c r="M95" t="n">
         <v>105.961</v>
       </c>
-      <c r="N95" t="inlineStr"/>
       <c r="O95" t="n">
         <v>1.875</v>
       </c>
       <c r="P95" s="1" t="n">
-        <v>46141.56863921279</v>
+        <v>46141.56863921296</v>
+      </c>
+      <c r="Q95" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -5560,7 +5982,6 @@
       <c r="I96" t="n">
         <v>2149607936</v>
       </c>
-      <c r="J96" t="inlineStr"/>
       <c r="K96" t="n">
         <v>-1.9929601</v>
       </c>
@@ -5570,12 +5991,14 @@
       <c r="M96" t="n">
         <v>106.529</v>
       </c>
-      <c r="N96" t="inlineStr"/>
       <c r="O96" t="n">
         <v>3</v>
       </c>
       <c r="P96" s="1" t="n">
-        <v>46141.56865947042</v>
+        <v>46141.56865946759</v>
+      </c>
+      <c r="Q96" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="97">
@@ -5624,12 +6047,14 @@
       <c r="M97" t="n">
         <v>98.91</v>
       </c>
-      <c r="N97" t="inlineStr"/>
       <c r="O97" t="n">
         <v>3.14286</v>
       </c>
       <c r="P97" s="1" t="n">
-        <v>46141.56867851826</v>
+        <v>46141.56867851852</v>
+      </c>
+      <c r="Q97" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="98">
@@ -5666,20 +6091,20 @@
       <c r="I98" t="n">
         <v>12016120832</v>
       </c>
-      <c r="J98" t="inlineStr"/>
       <c r="K98" t="n">
         <v>0</v>
       </c>
-      <c r="L98" t="inlineStr"/>
       <c r="M98" t="n">
         <v>0.098</v>
       </c>
-      <c r="N98" t="inlineStr"/>
       <c r="O98" t="n">
         <v>1.85</v>
       </c>
       <c r="P98" s="1" t="n">
-        <v>46141.56869833025</v>
+        <v>46141.56869833334</v>
+      </c>
+      <c r="Q98" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -5716,7 +6141,6 @@
       <c r="I99" t="n">
         <v>20343224320</v>
       </c>
-      <c r="J99" t="inlineStr"/>
       <c r="K99" t="n">
         <v>-0.67681</v>
       </c>
@@ -5726,12 +6150,14 @@
       <c r="M99" t="n">
         <v>113.082</v>
       </c>
-      <c r="N99" t="inlineStr"/>
       <c r="O99" t="n">
         <v>2.57692</v>
       </c>
       <c r="P99" s="1" t="n">
-        <v>46141.56871807512</v>
+        <v>46141.56871807871</v>
+      </c>
+      <c r="Q99" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="100">
@@ -5768,7 +6194,6 @@
       <c r="I100" t="n">
         <v>6708422656</v>
       </c>
-      <c r="J100" t="inlineStr"/>
       <c r="K100" t="n">
         <v>0</v>
       </c>
@@ -5778,12 +6203,14 @@
       <c r="M100" t="n">
         <v>5.099</v>
       </c>
-      <c r="N100" t="inlineStr"/>
       <c r="O100" t="n">
         <v>1.33333</v>
       </c>
       <c r="P100" s="1" t="n">
-        <v>46141.56873873805</v>
+        <v>46141.56873873842</v>
+      </c>
+      <c r="Q100" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="101">
@@ -5829,7 +6256,6 @@
       <c r="L101" t="n">
         <v>0.057</v>
       </c>
-      <c r="M101" t="inlineStr"/>
       <c r="N101" t="n">
         <v>2.21</v>
       </c>
@@ -5837,7 +6263,10 @@
         <v>1.88</v>
       </c>
       <c r="P101" s="1" t="n">
-        <v>46141.56876109292</v>
+        <v>46141.56876108796</v>
+      </c>
+      <c r="Q101" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="102">
@@ -5893,7 +6322,10 @@
         <v>2.22222</v>
       </c>
       <c r="P102" s="1" t="n">
-        <v>46141.56878241758</v>
+        <v>46141.56878241898</v>
+      </c>
+      <c r="Q102" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="103">
@@ -5939,7 +6371,6 @@
       <c r="L103" t="n">
         <v>-0.188</v>
       </c>
-      <c r="M103" t="inlineStr"/>
       <c r="N103" t="n">
         <v>3.66</v>
       </c>
@@ -5947,7 +6378,10 @@
         <v>2.64706</v>
       </c>
       <c r="P103" s="1" t="n">
-        <v>46141.56880281446</v>
+        <v>46141.5688028125</v>
+      </c>
+      <c r="Q103" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="104">
@@ -6003,7 +6437,10 @@
         <v>1.33333</v>
       </c>
       <c r="P104" s="1" t="n">
-        <v>46141.5688226725</v>
+        <v>46141.56882267361</v>
+      </c>
+      <c r="Q104" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -6059,7 +6496,10 @@
         <v>2.5</v>
       </c>
       <c r="P105" s="1" t="n">
-        <v>46141.5688428971</v>
+        <v>46141.56884289352</v>
+      </c>
+      <c r="Q105" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -6115,7 +6555,10 @@
         <v>1.92308</v>
       </c>
       <c r="P106" s="1" t="n">
-        <v>46141.56886373407</v>
+        <v>46141.56886373842</v>
+      </c>
+      <c r="Q106" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="107">
@@ -6171,7 +6614,10 @@
         <v>1.41667</v>
       </c>
       <c r="P107" s="1" t="n">
-        <v>46141.56888376275</v>
+        <v>46141.56888376157</v>
+      </c>
+      <c r="Q107" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="108">
@@ -6220,10 +6666,11 @@
       <c r="M108" t="n">
         <v>0.152</v>
       </c>
-      <c r="N108" t="inlineStr"/>
-      <c r="O108" t="inlineStr"/>
       <c r="P108" s="1" t="n">
-        <v>46141.56890335792</v>
+        <v>46141.56890335648</v>
+      </c>
+      <c r="Q108" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="109">
@@ -6279,7 +6726,10 @@
         <v>1.8</v>
       </c>
       <c r="P109" s="1" t="n">
-        <v>46141.5689243097</v>
+        <v>46141.56892430555</v>
+      </c>
+      <c r="Q109" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="110">
@@ -6316,7 +6766,6 @@
       <c r="I110" t="n">
         <v>461759904</v>
       </c>
-      <c r="J110" t="inlineStr"/>
       <c r="K110" t="n">
         <v>-0.116210006</v>
       </c>
@@ -6326,12 +6775,14 @@
       <c r="M110" t="n">
         <v>6.794</v>
       </c>
-      <c r="N110" t="inlineStr"/>
       <c r="O110" t="n">
         <v>3</v>
       </c>
       <c r="P110" s="1" t="n">
-        <v>46141.56894407523</v>
+        <v>46141.56894407408</v>
+      </c>
+      <c r="Q110" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="111">
@@ -6387,7 +6838,10 @@
         <v>2.66667</v>
       </c>
       <c r="P111" s="1" t="n">
-        <v>46141.56897168397</v>
+        <v>46141.56897167824</v>
+      </c>
+      <c r="Q111" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="112">
@@ -6438,10 +6892,11 @@
       <c r="M112" t="n">
         <v>160.208</v>
       </c>
-      <c r="N112" t="inlineStr"/>
-      <c r="O112" t="inlineStr"/>
       <c r="P112" s="1" t="n">
-        <v>46141.56899079706</v>
+        <v>46141.56899079861</v>
+      </c>
+      <c r="Q112" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="113">
@@ -6478,7 +6933,6 @@
       <c r="I113" t="n">
         <v>35740590080</v>
       </c>
-      <c r="J113" t="inlineStr"/>
       <c r="K113" t="n">
         <v>-0.07943</v>
       </c>
@@ -6495,7 +6949,10 @@
         <v>2</v>
       </c>
       <c r="P113" s="1" t="n">
-        <v>46141.56901294637</v>
+        <v>46141.56901295139</v>
+      </c>
+      <c r="Q113" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="114">
@@ -6551,7 +7008,10 @@
         <v>2.38095</v>
       </c>
       <c r="P114" s="1" t="n">
-        <v>46141.56903222325</v>
+        <v>46141.56903222222</v>
+      </c>
+      <c r="Q114" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="115">
@@ -6597,7 +7057,6 @@
       <c r="L115" t="n">
         <v>0.054</v>
       </c>
-      <c r="M115" t="inlineStr"/>
       <c r="N115" t="n">
         <v>3.1</v>
       </c>
@@ -6605,7 +7064,10 @@
         <v>2.23077</v>
       </c>
       <c r="P115" s="1" t="n">
-        <v>46141.56905372028</v>
+        <v>46141.56905371528</v>
+      </c>
+      <c r="Q115" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="116">
@@ -6661,7 +7123,10 @@
         <v>2.27778</v>
       </c>
       <c r="P116" s="1" t="n">
-        <v>46141.56907392049</v>
+        <v>46141.56907392361</v>
+      </c>
+      <c r="Q116" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="117">
@@ -6717,7 +7182,10 @@
         <v>1.8</v>
       </c>
       <c r="P117" s="1" t="n">
-        <v>46141.56909274137</v>
+        <v>46141.56909274306</v>
+      </c>
+      <c r="Q117" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="118">
@@ -6773,7 +7241,10 @@
         <v>1.67857</v>
       </c>
       <c r="P118" s="1" t="n">
-        <v>46141.56911292209</v>
+        <v>46141.56911291667</v>
+      </c>
+      <c r="Q118" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="119">
@@ -6810,7 +7281,6 @@
       <c r="I119" t="n">
         <v>1173315200</v>
       </c>
-      <c r="J119" t="inlineStr"/>
       <c r="K119" t="n">
         <v>-1.08002</v>
       </c>
@@ -6820,10 +7290,11 @@
       <c r="M119" t="n">
         <v>6.993</v>
       </c>
-      <c r="N119" t="inlineStr"/>
-      <c r="O119" t="inlineStr"/>
       <c r="P119" s="1" t="n">
-        <v>46141.56913297368</v>
+        <v>46141.56913297454</v>
+      </c>
+      <c r="Q119" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="120">
@@ -6860,7 +7331,6 @@
       <c r="I120" t="n">
         <v>2808288000</v>
       </c>
-      <c r="J120" t="inlineStr"/>
       <c r="K120" t="n">
         <v>-0.29490998</v>
       </c>
@@ -6877,7 +7347,10 @@
         <v>3.21429</v>
       </c>
       <c r="P120" s="1" t="n">
-        <v>46141.56915314506</v>
+        <v>46141.56915314815</v>
+      </c>
+      <c r="Q120" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="121">
@@ -6923,13 +7396,14 @@
       <c r="L121" t="n">
         <v>-0.435</v>
       </c>
-      <c r="M121" t="inlineStr"/>
       <c r="N121" t="n">
         <v>29.16</v>
       </c>
-      <c r="O121" t="inlineStr"/>
       <c r="P121" s="1" t="n">
-        <v>46141.56917259377</v>
+        <v>46141.56917259259</v>
+      </c>
+      <c r="Q121" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="122">
@@ -6985,7 +7459,10 @@
         <v>2.93333</v>
       </c>
       <c r="P122" s="1" t="n">
-        <v>46141.56919397999</v>
+        <v>46141.56919398148</v>
+      </c>
+      <c r="Q122" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="123">
@@ -7034,12 +7511,14 @@
       <c r="M123" t="n">
         <v>22.558</v>
       </c>
-      <c r="N123" t="inlineStr"/>
       <c r="O123" t="n">
         <v>2.2</v>
       </c>
       <c r="P123" s="1" t="n">
-        <v>46141.56921343506</v>
+        <v>46141.5692134375</v>
+      </c>
+      <c r="Q123" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="124">
@@ -7095,7 +7574,10 @@
         <v>1.42857</v>
       </c>
       <c r="P124" s="1" t="n">
-        <v>46141.56923300199</v>
+        <v>46141.56923299769</v>
+      </c>
+      <c r="Q124" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="125">
@@ -7147,9 +7629,11 @@
       <c r="N125" t="n">
         <v>1.49</v>
       </c>
-      <c r="O125" t="inlineStr"/>
       <c r="P125" s="1" t="n">
-        <v>46141.5692517825</v>
+        <v>46141.56925178241</v>
+      </c>
+      <c r="Q125" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="126">
@@ -7205,7 +7689,10 @@
         <v>1.7</v>
       </c>
       <c r="P126" s="1" t="n">
-        <v>46141.5692716536</v>
+        <v>46141.56927165509</v>
+      </c>
+      <c r="Q126" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="127">
@@ -7242,7 +7729,6 @@
       <c r="I127" t="n">
         <v>131317704</v>
       </c>
-      <c r="J127" t="inlineStr"/>
       <c r="K127" t="n">
         <v>-0.07337</v>
       </c>
@@ -7255,9 +7741,11 @@
       <c r="N127" t="n">
         <v>2.45</v>
       </c>
-      <c r="O127" t="inlineStr"/>
       <c r="P127" s="1" t="n">
-        <v>46141.56929013147</v>
+        <v>46141.56929012731</v>
+      </c>
+      <c r="Q127" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="128">
@@ -7313,7 +7801,10 @@
         <v>2.52174</v>
       </c>
       <c r="P128" s="1" t="n">
-        <v>46141.56930966363</v>
+        <v>46141.56930966435</v>
+      </c>
+      <c r="Q128" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="129">
@@ -7369,7 +7860,10 @@
         <v>2.14286</v>
       </c>
       <c r="P129" s="1" t="n">
-        <v>46141.56932978283</v>
+        <v>46141.56932978009</v>
+      </c>
+      <c r="Q129" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="130">
@@ -7418,12 +7912,14 @@
       <c r="M130" t="n">
         <v>51.016</v>
       </c>
-      <c r="N130" t="inlineStr"/>
       <c r="O130" t="n">
         <v>1.58333</v>
       </c>
       <c r="P130" s="1" t="n">
-        <v>46141.56935038343</v>
+        <v>46141.56935038194</v>
+      </c>
+      <c r="Q130" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="131">
@@ -7479,7 +7975,10 @@
         <v>2.75</v>
       </c>
       <c r="P131" s="1" t="n">
-        <v>46141.56937044267</v>
+        <v>46141.56937043981</v>
+      </c>
+      <c r="Q131" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="132">
@@ -7516,7 +8015,6 @@
       <c r="I132" t="n">
         <v>30502426624</v>
       </c>
-      <c r="J132" t="inlineStr"/>
       <c r="K132" t="n">
         <v>-0.11356</v>
       </c>
@@ -7529,9 +8027,11 @@
       <c r="N132" t="n">
         <v>3.41</v>
       </c>
-      <c r="O132" t="inlineStr"/>
       <c r="P132" s="1" t="n">
-        <v>46141.56939407958</v>
+        <v>46141.56939407407</v>
+      </c>
+      <c r="Q132" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="133">
@@ -7582,10 +8082,11 @@
       <c r="M133" t="n">
         <v>18.299</v>
       </c>
-      <c r="N133" t="inlineStr"/>
-      <c r="O133" t="inlineStr"/>
       <c r="P133" s="1" t="n">
-        <v>46141.56941284241</v>
+        <v>46141.56941284722</v>
+      </c>
+      <c r="Q133" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="134">
@@ -7641,7 +8142,10 @@
         <v>1.95833</v>
       </c>
       <c r="P134" s="1" t="n">
-        <v>46141.56943320875</v>
+        <v>46141.56943320602</v>
+      </c>
+      <c r="Q134" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="135">
@@ -7697,7 +8201,10 @@
         <v>1.77778</v>
       </c>
       <c r="P135" s="1" t="n">
-        <v>46141.56945283774</v>
+        <v>46141.56945283565</v>
+      </c>
+      <c r="Q135" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="136">
@@ -7734,7 +8241,6 @@
       <c r="I136" t="n">
         <v>392019680</v>
       </c>
-      <c r="J136" t="inlineStr"/>
       <c r="K136" t="n">
         <v>-1.28623</v>
       </c>
@@ -7744,10 +8250,11 @@
       <c r="M136" t="n">
         <v>5.971</v>
       </c>
-      <c r="N136" t="inlineStr"/>
-      <c r="O136" t="inlineStr"/>
       <c r="P136" s="1" t="n">
-        <v>46141.56947197575</v>
+        <v>46141.56947197916</v>
+      </c>
+      <c r="Q136" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="137">
@@ -7784,7 +8291,6 @@
       <c r="I137" t="n">
         <v>100505608</v>
       </c>
-      <c r="J137" t="inlineStr"/>
       <c r="K137" t="n">
         <v>-0.04247</v>
       </c>
@@ -7794,10 +8300,11 @@
       <c r="M137" t="n">
         <v>274.044</v>
       </c>
-      <c r="N137" t="inlineStr"/>
-      <c r="O137" t="inlineStr"/>
       <c r="P137" s="1" t="n">
-        <v>46141.56949054063</v>
+        <v>46141.56949054398</v>
+      </c>
+      <c r="Q137" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="138">
@@ -7851,9 +8358,11 @@
       <c r="N138" t="n">
         <v>4.17</v>
       </c>
-      <c r="O138" t="inlineStr"/>
       <c r="P138" s="1" t="n">
-        <v>46141.56951074093</v>
+        <v>46141.56951074074</v>
+      </c>
+      <c r="Q138" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="139">
@@ -7909,7 +8418,10 @@
         <v>2.27778</v>
       </c>
       <c r="P139" s="1" t="n">
-        <v>46141.5695314884</v>
+        <v>46141.56953149306</v>
+      </c>
+      <c r="Q139" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="140">
@@ -7965,7 +8477,10 @@
         <v>1.68421</v>
       </c>
       <c r="P140" s="1" t="n">
-        <v>46141.56955110964</v>
+        <v>46141.56955111111</v>
+      </c>
+      <c r="Q140" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="141">
@@ -8021,7 +8536,10 @@
         <v>2.78571</v>
       </c>
       <c r="P141" s="1" t="n">
-        <v>46141.56957163491</v>
+        <v>46141.56957163195</v>
+      </c>
+      <c r="Q141" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="142">
@@ -8055,21 +8573,20 @@
       <c r="H142" t="n">
         <v>1</v>
       </c>
-      <c r="I142" t="inlineStr"/>
       <c r="J142" t="n">
         <v>15.294118</v>
       </c>
       <c r="K142" t="n">
         <v>0.0728</v>
       </c>
-      <c r="L142" t="inlineStr"/>
       <c r="M142" t="n">
         <v>56.597</v>
       </c>
-      <c r="N142" t="inlineStr"/>
-      <c r="O142" t="inlineStr"/>
       <c r="P142" s="1" t="n">
-        <v>46141.56959023359</v>
+        <v>46141.56959023148</v>
+      </c>
+      <c r="Q142" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="143">
@@ -8125,7 +8642,10 @@
         <v>2.8</v>
       </c>
       <c r="P143" s="1" t="n">
-        <v>46141.56961074247</v>
+        <v>46141.56961074074</v>
+      </c>
+      <c r="Q143" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="144">
@@ -8181,7 +8701,10 @@
         <v>1.57143</v>
       </c>
       <c r="P144" s="1" t="n">
-        <v>46141.56963184423</v>
+        <v>46141.56963184028</v>
+      </c>
+      <c r="Q144" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="145">
@@ -8233,9 +8756,11 @@
       <c r="N145" t="n">
         <v>1.93</v>
       </c>
-      <c r="O145" t="inlineStr"/>
       <c r="P145" s="1" t="n">
-        <v>46141.569653132</v>
+        <v>46141.56965313658</v>
+      </c>
+      <c r="Q145" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="146">
@@ -8291,7 +8816,10 @@
         <v>2.14286</v>
       </c>
       <c r="P146" s="1" t="n">
-        <v>46141.56967231283</v>
+        <v>46141.56967231481</v>
+      </c>
+      <c r="Q146" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="147">
@@ -8328,7 +8856,6 @@
       <c r="I147" t="n">
         <v>304989248</v>
       </c>
-      <c r="J147" t="inlineStr"/>
       <c r="K147" t="n">
         <v>-0.12968999</v>
       </c>
@@ -8338,10 +8865,11 @@
       <c r="M147" t="n">
         <v>28.308</v>
       </c>
-      <c r="N147" t="inlineStr"/>
-      <c r="O147" t="inlineStr"/>
       <c r="P147" s="1" t="n">
-        <v>46141.56969135603</v>
+        <v>46141.56969135417</v>
+      </c>
+      <c r="Q147" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="148">
@@ -8378,7 +8906,6 @@
       <c r="I148" t="n">
         <v>5669197312</v>
       </c>
-      <c r="J148" t="inlineStr"/>
       <c r="K148" t="n">
         <v>-0.05568</v>
       </c>
@@ -8388,12 +8915,14 @@
       <c r="M148" t="n">
         <v>257.86</v>
       </c>
-      <c r="N148" t="inlineStr"/>
       <c r="O148" t="n">
         <v>2.16667</v>
       </c>
       <c r="P148" s="1" t="n">
-        <v>46141.56971138868</v>
+        <v>46141.56971138889</v>
+      </c>
+      <c r="Q148" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="149">
@@ -8442,12 +8971,14 @@
       <c r="M149" t="n">
         <v>302.121</v>
       </c>
-      <c r="N149" t="inlineStr"/>
       <c r="O149" t="n">
         <v>1.90909</v>
       </c>
       <c r="P149" s="1" t="n">
-        <v>46141.56973162742</v>
+        <v>46141.56973163194</v>
+      </c>
+      <c r="Q149" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="150">
@@ -8484,7 +9015,6 @@
       <c r="I150" t="n">
         <v>911945408</v>
       </c>
-      <c r="J150" t="inlineStr"/>
       <c r="K150" t="n">
         <v>-0.1313</v>
       </c>
@@ -8494,12 +9024,14 @@
       <c r="M150" t="n">
         <v>55.019</v>
       </c>
-      <c r="N150" t="inlineStr"/>
       <c r="O150" t="n">
         <v>2</v>
       </c>
       <c r="P150" s="1" t="n">
-        <v>46141.56975115577</v>
+        <v>46141.56975115741</v>
+      </c>
+      <c r="Q150" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="151">
@@ -8536,7 +9068,6 @@
       <c r="I151" t="n">
         <v>3656669440</v>
       </c>
-      <c r="J151" t="inlineStr"/>
       <c r="K151" t="n">
         <v>-0.088470004</v>
       </c>
@@ -8553,7 +9084,10 @@
         <v>2.47059</v>
       </c>
       <c r="P151" s="1" t="n">
-        <v>46141.56977121966</v>
+        <v>46141.56977121528</v>
+      </c>
+      <c r="Q151" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="152">
@@ -8605,9 +9139,11 @@
       <c r="N152" t="n">
         <v>2.51</v>
       </c>
-      <c r="O152" t="inlineStr"/>
       <c r="P152" s="1" t="n">
-        <v>46141.56979221055</v>
+        <v>46141.56979221065</v>
+      </c>
+      <c r="Q152" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="153">
@@ -8663,7 +9199,10 @@
         <v>2.35294</v>
       </c>
       <c r="P153" s="1" t="n">
-        <v>46141.56981121295</v>
+        <v>46141.56981121527</v>
+      </c>
+      <c r="Q153" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="154">
@@ -8715,9 +9254,11 @@
       <c r="N154" t="n">
         <v>8.19</v>
       </c>
-      <c r="O154" t="inlineStr"/>
       <c r="P154" s="1" t="n">
-        <v>46141.56983476011</v>
+        <v>46141.56983475694</v>
+      </c>
+      <c r="Q154" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="155">
@@ -8769,9 +9310,11 @@
       <c r="N155" t="n">
         <v>4.23</v>
       </c>
-      <c r="O155" t="inlineStr"/>
       <c r="P155" s="1" t="n">
-        <v>46141.56985569723</v>
+        <v>46141.56985569445</v>
+      </c>
+      <c r="Q155" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="156">
@@ -8825,9 +9368,11 @@
       <c r="N156" t="n">
         <v>0.13</v>
       </c>
-      <c r="O156" t="inlineStr"/>
       <c r="P156" s="1" t="n">
-        <v>46141.56987531012</v>
+        <v>46141.5698753125</v>
+      </c>
+      <c r="Q156" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="157">
@@ -8870,7 +9415,6 @@
       <c r="K157" t="n">
         <v>0.06884</v>
       </c>
-      <c r="L157" t="inlineStr"/>
       <c r="M157" t="n">
         <v>39.741</v>
       </c>
@@ -8881,7 +9425,10 @@
         <v>1.375</v>
       </c>
       <c r="P157" s="1" t="n">
-        <v>46141.56989510199</v>
+        <v>46141.56989510416</v>
+      </c>
+      <c r="Q157" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="158">
@@ -8937,7 +9484,10 @@
         <v>2.70588</v>
       </c>
       <c r="P158" s="1" t="n">
-        <v>46141.56991386183</v>
+        <v>46141.56991386574</v>
+      </c>
+      <c r="Q158" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="159">
@@ -8993,7 +9543,10 @@
         <v>2.33333</v>
       </c>
       <c r="P159" s="1" t="n">
-        <v>46141.56993454911</v>
+        <v>46141.56993454861</v>
+      </c>
+      <c r="Q159" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="160">
@@ -9045,9 +9598,11 @@
       <c r="N160" t="n">
         <v>3.53</v>
       </c>
-      <c r="O160" t="inlineStr"/>
       <c r="P160" s="1" t="n">
-        <v>46141.56995363227</v>
+        <v>46141.56995363426</v>
+      </c>
+      <c r="Q160" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="161">
@@ -9098,10 +9653,11 @@
       <c r="M161" t="n">
         <v>15.059</v>
       </c>
-      <c r="N161" t="inlineStr"/>
-      <c r="O161" t="inlineStr"/>
       <c r="P161" s="1" t="n">
-        <v>46141.56997171807</v>
+        <v>46141.56997171296</v>
+      </c>
+      <c r="Q161" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="162">
@@ -9157,7 +9713,10 @@
         <v>1</v>
       </c>
       <c r="P162" s="1" t="n">
-        <v>46141.56999087808</v>
+        <v>46141.56999087963</v>
+      </c>
+      <c r="Q162" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="163">
@@ -9213,7 +9772,10 @@
         <v>2.92857</v>
       </c>
       <c r="P163" s="1" t="n">
-        <v>46141.5700126281</v>
+        <v>46141.57001262732</v>
+      </c>
+      <c r="Q163" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="164">
@@ -9264,10 +9826,11 @@
       <c r="M164" t="n">
         <v>0.446</v>
       </c>
-      <c r="N164" t="inlineStr"/>
-      <c r="O164" t="inlineStr"/>
       <c r="P164" s="1" t="n">
-        <v>46141.57003033334</v>
+        <v>46141.57003033565</v>
+      </c>
+      <c r="Q164" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="165">
@@ -9323,7 +9886,10 @@
         <v>2.82353</v>
       </c>
       <c r="P165" s="1" t="n">
-        <v>46141.57005062615</v>
+        <v>46141.570050625</v>
+      </c>
+      <c r="Q165" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="166">
@@ -9379,7 +9945,10 @@
         <v>1.91667</v>
       </c>
       <c r="P166" s="1" t="n">
-        <v>46141.57007150993</v>
+        <v>46141.57007150463</v>
+      </c>
+      <c r="Q166" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="167">
@@ -9416,7 +9985,6 @@
       <c r="I167" t="n">
         <v>800832896</v>
       </c>
-      <c r="J167" t="inlineStr"/>
       <c r="K167" t="n">
         <v>-0.011080001</v>
       </c>
@@ -9429,9 +9997,11 @@
       <c r="N167" t="n">
         <v>8.1</v>
       </c>
-      <c r="O167" t="inlineStr"/>
       <c r="P167" s="1" t="n">
-        <v>46141.57009156116</v>
+        <v>46141.5700915625</v>
+      </c>
+      <c r="Q167" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="168">
@@ -9480,10 +10050,11 @@
       <c r="M168" t="n">
         <v>36.985</v>
       </c>
-      <c r="N168" t="inlineStr"/>
-      <c r="O168" t="inlineStr"/>
       <c r="P168" s="1" t="n">
-        <v>46141.57011082564</v>
+        <v>46141.57011082176</v>
+      </c>
+      <c r="Q168" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="169">
@@ -9535,9 +10106,11 @@
       <c r="N169" t="n">
         <v>0.4</v>
       </c>
-      <c r="O169" t="inlineStr"/>
       <c r="P169" s="1" t="n">
-        <v>46141.57013118337</v>
+        <v>46141.57013118055</v>
+      </c>
+      <c r="Q169" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="170">
@@ -9593,7 +10166,10 @@
         <v>1.70588</v>
       </c>
       <c r="P170" s="1" t="n">
-        <v>46141.5701497537</v>
+        <v>46141.57014975695</v>
+      </c>
+      <c r="Q170" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="171">
@@ -9649,7 +10225,10 @@
         <v>1.57143</v>
       </c>
       <c r="P171" s="1" t="n">
-        <v>46141.57016931995</v>
+        <v>46141.57016931713</v>
+      </c>
+      <c r="Q171" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="172">
@@ -9686,16 +10265,14 @@
       <c r="I172" t="n">
         <v>164582096</v>
       </c>
-      <c r="J172" t="inlineStr"/>
       <c r="K172" t="n">
         <v>0</v>
       </c>
-      <c r="L172" t="inlineStr"/>
-      <c r="M172" t="inlineStr"/>
-      <c r="N172" t="inlineStr"/>
-      <c r="O172" t="inlineStr"/>
       <c r="P172" s="1" t="n">
-        <v>46141.57018717727</v>
+        <v>46141.57018717592</v>
+      </c>
+      <c r="Q172" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="173">
@@ -9747,9 +10324,11 @@
       <c r="N173" t="n">
         <v>11.13</v>
       </c>
-      <c r="O173" t="inlineStr"/>
       <c r="P173" s="1" t="n">
-        <v>46141.57020701846</v>
+        <v>46141.57020701389</v>
+      </c>
+      <c r="Q173" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="174">
@@ -9786,7 +10365,6 @@
       <c r="I174" t="n">
         <v>7426793472</v>
       </c>
-      <c r="J174" t="inlineStr"/>
       <c r="K174" t="n">
         <v>-0.01805</v>
       </c>
@@ -9803,7 +10381,10 @@
         <v>1.90909</v>
       </c>
       <c r="P174" s="1" t="n">
-        <v>46141.57022655335</v>
+        <v>46141.57022655092</v>
+      </c>
+      <c r="Q174" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="175">
@@ -9859,7 +10440,10 @@
         <v>2.45</v>
       </c>
       <c r="P175" s="1" t="n">
-        <v>46141.5702470997</v>
+        <v>46141.57024709491</v>
+      </c>
+      <c r="Q175" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="176">
@@ -9896,7 +10480,6 @@
       <c r="I176" t="n">
         <v>3700950784</v>
       </c>
-      <c r="J176" t="inlineStr"/>
       <c r="K176" t="n">
         <v>-2.29828</v>
       </c>
@@ -9906,10 +10489,11 @@
       <c r="M176" t="n">
         <v>99.38800000000001</v>
       </c>
-      <c r="N176" t="inlineStr"/>
-      <c r="O176" t="inlineStr"/>
       <c r="P176" s="1" t="n">
-        <v>46141.57027110815</v>
+        <v>46141.57027111111</v>
+      </c>
+      <c r="Q176" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="177">
@@ -9965,7 +10549,10 @@
         <v>2.42857</v>
       </c>
       <c r="P177" s="1" t="n">
-        <v>46141.57028995062</v>
+        <v>46141.57028995371</v>
+      </c>
+      <c r="Q177" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="178">
@@ -10021,7 +10608,10 @@
         <v>1.63636</v>
       </c>
       <c r="P178" s="1" t="n">
-        <v>46141.57031090683</v>
+        <v>46141.57031090277</v>
+      </c>
+      <c r="Q178" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="179">
@@ -10073,9 +10663,11 @@
       <c r="N179" t="n">
         <v>4.96</v>
       </c>
-      <c r="O179" t="inlineStr"/>
       <c r="P179" s="1" t="n">
-        <v>46141.57033069798</v>
+        <v>46141.57033069444</v>
+      </c>
+      <c r="Q179" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="180">
@@ -10131,7 +10723,10 @@
         <v>2.13333</v>
       </c>
       <c r="P180" s="1" t="n">
-        <v>46141.57036827405</v>
+        <v>46141.57036827546</v>
+      </c>
+      <c r="Q180" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="181">
@@ -10168,7 +10763,6 @@
       <c r="I181" t="n">
         <v>147997472</v>
       </c>
-      <c r="J181" t="inlineStr"/>
       <c r="K181" t="n">
         <v>0</v>
       </c>
@@ -10178,10 +10772,11 @@
       <c r="M181" t="n">
         <v>33.739</v>
       </c>
-      <c r="N181" t="inlineStr"/>
-      <c r="O181" t="inlineStr"/>
       <c r="P181" s="1" t="n">
-        <v>46141.57038609061</v>
+        <v>46141.57038608797</v>
+      </c>
+      <c r="Q181" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="182">
@@ -10237,7 +10832,10 @@
         <v>3</v>
       </c>
       <c r="P182" s="1" t="n">
-        <v>46141.57040543285</v>
+        <v>46141.57040542824</v>
+      </c>
+      <c r="Q182" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="183">
@@ -10286,10 +10884,11 @@
       <c r="M183" t="n">
         <v>9.481</v>
       </c>
-      <c r="N183" t="inlineStr"/>
-      <c r="O183" t="inlineStr"/>
       <c r="P183" s="1" t="n">
-        <v>46141.57042507545</v>
+        <v>46141.57042508102</v>
+      </c>
+      <c r="Q183" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="184">
@@ -10326,7 +10925,6 @@
       <c r="I184" t="n">
         <v>548996672</v>
       </c>
-      <c r="J184" t="inlineStr"/>
       <c r="K184" t="n">
         <v>-0.09315</v>
       </c>
@@ -10336,12 +10934,14 @@
       <c r="M184" t="n">
         <v>54.711</v>
       </c>
-      <c r="N184" t="inlineStr"/>
       <c r="O184" t="n">
         <v>3</v>
       </c>
       <c r="P184" s="1" t="n">
-        <v>46141.57044379748</v>
+        <v>46141.5704437963</v>
+      </c>
+      <c r="Q184" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="185">
@@ -10393,9 +10993,11 @@
       <c r="N185" t="n">
         <v>4.07</v>
       </c>
-      <c r="O185" t="inlineStr"/>
       <c r="P185" s="1" t="n">
-        <v>46141.57046319287</v>
+        <v>46141.57046319445</v>
+      </c>
+      <c r="Q185" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="186">
@@ -10432,7 +11034,6 @@
       <c r="I186" t="n">
         <v>1574956544</v>
       </c>
-      <c r="J186" t="inlineStr"/>
       <c r="K186" t="n">
         <v>-0.10170999</v>
       </c>
@@ -10449,7 +11050,10 @@
         <v>2.875</v>
       </c>
       <c r="P186" s="1" t="n">
-        <v>46141.57048382551</v>
+        <v>46141.57048383102</v>
+      </c>
+      <c r="Q186" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="187">
@@ -10505,7 +11109,10 @@
         <v>1.11111</v>
       </c>
       <c r="P187" s="1" t="n">
-        <v>46141.57050614237</v>
+        <v>46141.57050614584</v>
+      </c>
+      <c r="Q187" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="188">
@@ -10559,9 +11166,11 @@
       <c r="N188" t="n">
         <v>0.77</v>
       </c>
-      <c r="O188" t="inlineStr"/>
       <c r="P188" s="1" t="n">
-        <v>46141.57052633814</v>
+        <v>46141.57052634259</v>
+      </c>
+      <c r="Q188" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="189">
@@ -10613,9 +11222,11 @@
       <c r="N189" t="n">
         <v>0.53</v>
       </c>
-      <c r="O189" t="inlineStr"/>
       <c r="P189" s="1" t="n">
-        <v>46141.57054552021</v>
+        <v>46141.57054552083</v>
+      </c>
+      <c r="Q189" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="190">
@@ -10666,10 +11277,11 @@
       <c r="M190" t="n">
         <v>150.23</v>
       </c>
-      <c r="N190" t="inlineStr"/>
-      <c r="O190" t="inlineStr"/>
       <c r="P190" s="1" t="n">
-        <v>46141.57056301158</v>
+        <v>46141.57056300926</v>
+      </c>
+      <c r="Q190" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="191">
@@ -10723,9 +11335,11 @@
       <c r="N191" t="n">
         <v>10.82</v>
       </c>
-      <c r="O191" t="inlineStr"/>
       <c r="P191" s="1" t="n">
-        <v>46141.57058260326</v>
+        <v>46141.57058260417</v>
+      </c>
+      <c r="Q191" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="192">
@@ -10777,9 +11391,11 @@
       <c r="N192" t="n">
         <v>0.97</v>
       </c>
-      <c r="O192" t="inlineStr"/>
       <c r="P192" s="1" t="n">
-        <v>46141.57060206303</v>
+        <v>46141.57060206019</v>
+      </c>
+      <c r="Q192" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="193">
@@ -10816,18 +11432,17 @@
       <c r="I193" t="n">
         <v>216299264</v>
       </c>
-      <c r="J193" t="inlineStr"/>
       <c r="K193" t="n">
         <v>0</v>
       </c>
       <c r="L193" t="n">
         <v>2.334</v>
       </c>
-      <c r="M193" t="inlineStr"/>
-      <c r="N193" t="inlineStr"/>
-      <c r="O193" t="inlineStr"/>
       <c r="P193" s="1" t="n">
-        <v>46141.57062078243</v>
+        <v>46141.57062078704</v>
+      </c>
+      <c r="Q193" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="194">
@@ -10870,7 +11485,6 @@
       <c r="K194" t="n">
         <v>0</v>
       </c>
-      <c r="L194" t="inlineStr"/>
       <c r="M194" t="n">
         <v>18.65</v>
       </c>
@@ -10881,7 +11495,10 @@
         <v>2.8</v>
       </c>
       <c r="P194" s="1" t="n">
-        <v>46141.5706425559</v>
+        <v>46141.57064255787</v>
+      </c>
+      <c r="Q194" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="195">
@@ -10924,16 +11541,17 @@
       <c r="K195" t="n">
         <v>0.083000004</v>
       </c>
-      <c r="L195" t="inlineStr"/>
       <c r="M195" t="n">
         <v>147.373</v>
       </c>
       <c r="N195" t="n">
         <v>4.09</v>
       </c>
-      <c r="O195" t="inlineStr"/>
       <c r="P195" s="1" t="n">
-        <v>46141.57066245314</v>
+        <v>46141.57066245371</v>
+      </c>
+      <c r="Q195" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="196">
@@ -10989,7 +11607,10 @@
         <v>2.22222</v>
       </c>
       <c r="P196" s="1" t="n">
-        <v>46141.57068323182</v>
+        <v>46141.57068322917</v>
+      </c>
+      <c r="Q196" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="197">
@@ -11026,16 +11647,14 @@
       <c r="I197" t="n">
         <v>175327264</v>
       </c>
-      <c r="J197" t="inlineStr"/>
       <c r="K197" t="n">
         <v>0</v>
       </c>
-      <c r="L197" t="inlineStr"/>
-      <c r="M197" t="inlineStr"/>
-      <c r="N197" t="inlineStr"/>
-      <c r="O197" t="inlineStr"/>
       <c r="P197" s="1" t="n">
-        <v>46141.57070030644</v>
+        <v>46141.57070030092</v>
+      </c>
+      <c r="Q197" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="198">
@@ -11091,7 +11710,10 @@
         <v>2.94444</v>
       </c>
       <c r="P198" s="1" t="n">
-        <v>46141.57072037186</v>
+        <v>46141.57072037037</v>
+      </c>
+      <c r="Q198" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="199">
@@ -11147,7 +11769,10 @@
         <v>2.46667</v>
       </c>
       <c r="P199" s="1" t="n">
-        <v>46141.57074065705</v>
+        <v>46141.57074065972</v>
+      </c>
+      <c r="Q199" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="200">
@@ -11184,7 +11809,6 @@
       <c r="I200" t="n">
         <v>1097003392</v>
       </c>
-      <c r="J200" t="inlineStr"/>
       <c r="K200" t="n">
         <v>0</v>
       </c>
@@ -11194,10 +11818,11 @@
       <c r="M200" t="n">
         <v>0.014</v>
       </c>
-      <c r="N200" t="inlineStr"/>
-      <c r="O200" t="inlineStr"/>
       <c r="P200" s="1" t="n">
-        <v>46141.57076269797</v>
+        <v>46141.57076269676</v>
+      </c>
+      <c r="Q200" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="201">
@@ -11246,12 +11871,14 @@
       <c r="M201" t="n">
         <v>35.374</v>
       </c>
-      <c r="N201" t="inlineStr"/>
       <c r="O201" t="n">
         <v>2.33333</v>
       </c>
       <c r="P201" s="1" t="n">
-        <v>46141.57078517501</v>
+        <v>46141.57078517361</v>
+      </c>
+      <c r="Q201" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="202">
@@ -11297,7 +11924,6 @@
       <c r="L202" t="n">
         <v>-0.035</v>
       </c>
-      <c r="M202" t="inlineStr"/>
       <c r="N202" t="n">
         <v>4.83</v>
       </c>
@@ -11305,7 +11931,10 @@
         <v>1.5</v>
       </c>
       <c r="P202" s="1" t="n">
-        <v>46141.57080566542</v>
+        <v>46141.57080565972</v>
+      </c>
+      <c r="Q202" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="203">
@@ -11342,7 +11971,6 @@
       <c r="I203" t="n">
         <v>80628015104</v>
       </c>
-      <c r="J203" t="inlineStr"/>
       <c r="K203" t="n">
         <v>-0.35215</v>
       </c>
@@ -11352,10 +11980,11 @@
       <c r="M203" t="n">
         <v>22.035</v>
       </c>
-      <c r="N203" t="inlineStr"/>
-      <c r="O203" t="inlineStr"/>
       <c r="P203" s="1" t="n">
-        <v>46141.57082511978</v>
+        <v>46141.57082511574</v>
+      </c>
+      <c r="Q203" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="204">
@@ -11401,7 +12030,6 @@
       <c r="L204" t="n">
         <v>0.024</v>
       </c>
-      <c r="M204" t="inlineStr"/>
       <c r="N204" t="n">
         <v>4.89</v>
       </c>
@@ -11409,7 +12037,10 @@
         <v>1.35294</v>
       </c>
       <c r="P204" s="1" t="n">
-        <v>46141.57084470437</v>
+        <v>46141.57084469908</v>
+      </c>
+      <c r="Q204" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="205">
@@ -11465,7 +12096,10 @@
         <v>2.07692</v>
       </c>
       <c r="P205" s="1" t="n">
-        <v>46141.57086430215</v>
+        <v>46141.57086430556</v>
+      </c>
+      <c r="Q205" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="206">
@@ -11511,7 +12145,6 @@
       <c r="L206" t="n">
         <v>0.063</v>
       </c>
-      <c r="M206" t="inlineStr"/>
       <c r="N206" t="n">
         <v>4.94</v>
       </c>
@@ -11519,7 +12152,10 @@
         <v>1.58824</v>
       </c>
       <c r="P206" s="1" t="n">
-        <v>46141.57088415316</v>
+        <v>46141.57088415509</v>
+      </c>
+      <c r="Q206" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="207">
@@ -11568,12 +12204,14 @@
       <c r="M207" t="n">
         <v>340.358</v>
       </c>
-      <c r="N207" t="inlineStr"/>
       <c r="O207" t="n">
         <v>4</v>
       </c>
       <c r="P207" s="1" t="n">
-        <v>46141.57090367302</v>
+        <v>46141.57090366898</v>
+      </c>
+      <c r="Q207" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="208">
@@ -11610,7 +12248,6 @@
       <c r="I208" t="n">
         <v>31066699776</v>
       </c>
-      <c r="J208" t="inlineStr"/>
       <c r="K208" t="n">
         <v>-0.19881001</v>
       </c>
@@ -11620,12 +12257,14 @@
       <c r="M208" t="n">
         <v>42.619</v>
       </c>
-      <c r="N208" t="inlineStr"/>
       <c r="O208" t="n">
         <v>1.4</v>
       </c>
       <c r="P208" s="1" t="n">
-        <v>46141.57092405634</v>
+        <v>46141.57092405092</v>
+      </c>
+      <c r="Q208" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="209">
@@ -11662,7 +12301,6 @@
       <c r="I209" t="n">
         <v>17889409024</v>
       </c>
-      <c r="J209" t="inlineStr"/>
       <c r="K209" t="n">
         <v>-0.27327</v>
       </c>
@@ -11672,12 +12310,14 @@
       <c r="M209" t="n">
         <v>403.094</v>
       </c>
-      <c r="N209" t="inlineStr"/>
       <c r="O209" t="n">
         <v>4</v>
       </c>
       <c r="P209" s="1" t="n">
-        <v>46141.57094426286</v>
+        <v>46141.57094425926</v>
+      </c>
+      <c r="Q209" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="210">
@@ -11729,9 +12369,11 @@
       <c r="N210" t="n">
         <v>4.49</v>
       </c>
-      <c r="O210" t="inlineStr"/>
       <c r="P210" s="1" t="n">
-        <v>46141.57096372766</v>
+        <v>46141.57096372685</v>
+      </c>
+      <c r="Q210" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="211">
@@ -11780,12 +12422,14 @@
       <c r="M211" t="n">
         <v>13.564</v>
       </c>
-      <c r="N211" t="inlineStr"/>
       <c r="O211" t="n">
         <v>1.75758</v>
       </c>
       <c r="P211" s="1" t="n">
-        <v>46141.57098395758</v>
+        <v>46141.57098395834</v>
+      </c>
+      <c r="Q211" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="212">
@@ -11834,12 +12478,14 @@
       <c r="M212" t="n">
         <v>3.506</v>
       </c>
-      <c r="N212" t="inlineStr"/>
       <c r="O212" t="n">
         <v>1.21429</v>
       </c>
       <c r="P212" s="1" t="n">
-        <v>46141.57100368169</v>
+        <v>46141.57100368055</v>
+      </c>
+      <c r="Q212" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="213">
@@ -11885,7 +12531,6 @@
       <c r="L213" t="n">
         <v>0.021</v>
       </c>
-      <c r="M213" t="inlineStr"/>
       <c r="N213" t="n">
         <v>4.52</v>
       </c>
@@ -11893,7 +12538,10 @@
         <v>1.88235</v>
       </c>
       <c r="P213" s="1" t="n">
-        <v>46141.57102279589</v>
+        <v>46141.57102280093</v>
+      </c>
+      <c r="Q213" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="214">
@@ -11949,7 +12597,10 @@
         <v>1.66667</v>
       </c>
       <c r="P214" s="1" t="n">
-        <v>46141.57104474979</v>
+        <v>46141.57104474537</v>
+      </c>
+      <c r="Q214" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="215">
@@ -12001,9 +12652,11 @@
       <c r="N215" t="n">
         <v>5.11</v>
       </c>
-      <c r="O215" t="inlineStr"/>
       <c r="P215" s="1" t="n">
-        <v>46141.57106521036</v>
+        <v>46141.57106520834</v>
+      </c>
+      <c r="Q215" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="216">
@@ -12052,10 +12705,11 @@
       <c r="M216" t="n">
         <v>318.913</v>
       </c>
-      <c r="N216" t="inlineStr"/>
-      <c r="O216" t="inlineStr"/>
       <c r="P216" s="1" t="n">
-        <v>46141.57108565</v>
+        <v>46141.57108564815</v>
+      </c>
+      <c r="Q216" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="217">
@@ -12104,10 +12758,11 @@
       <c r="M217" t="n">
         <v>4.859</v>
       </c>
-      <c r="N217" t="inlineStr"/>
-      <c r="O217" t="inlineStr"/>
       <c r="P217" s="1" t="n">
-        <v>46141.57110511984</v>
+        <v>46141.57110511574</v>
+      </c>
+      <c r="Q217" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="218">
@@ -12156,10 +12811,11 @@
       <c r="M218" t="n">
         <v>85.20699999999999</v>
       </c>
-      <c r="N218" t="inlineStr"/>
-      <c r="O218" t="inlineStr"/>
       <c r="P218" s="1" t="n">
-        <v>46141.57112390841</v>
+        <v>46141.57112391204</v>
+      </c>
+      <c r="Q218" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="219">
@@ -12215,7 +12871,10 @@
         <v>1.3125</v>
       </c>
       <c r="P219" s="1" t="n">
-        <v>46141.57114310608</v>
+        <v>46141.57114310185</v>
+      </c>
+      <c r="Q219" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="220">
@@ -12271,7 +12930,10 @@
         <v>1.83333</v>
       </c>
       <c r="P220" s="1" t="n">
-        <v>46141.57116232551</v>
+        <v>46141.57116232639</v>
+      </c>
+      <c r="Q220" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="221">
@@ -12327,7 +12989,10 @@
         <v>1.75</v>
       </c>
       <c r="P221" s="1" t="n">
-        <v>46141.57118196346</v>
+        <v>46141.57118196759</v>
+      </c>
+      <c r="Q221" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="222">
@@ -12383,7 +13048,10 @@
         <v>1.82353</v>
       </c>
       <c r="P222" s="1" t="n">
-        <v>46141.57120150926</v>
+        <v>46141.57120150463</v>
+      </c>
+      <c r="Q222" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="223">
@@ -12439,7 +13107,10 @@
         <v>1.88462</v>
       </c>
       <c r="P223" s="1" t="n">
-        <v>46141.57122141529</v>
+        <v>46141.57122141204</v>
+      </c>
+      <c r="Q223" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="224">
@@ -12476,7 +13147,6 @@
       <c r="I224" t="n">
         <v>106419732480</v>
       </c>
-      <c r="J224" t="inlineStr"/>
       <c r="K224" t="n">
         <v>-2.78559</v>
       </c>
@@ -12486,12 +13156,14 @@
       <c r="M224" t="n">
         <v>123.048</v>
       </c>
-      <c r="N224" t="inlineStr"/>
       <c r="O224" t="n">
         <v>1.30435</v>
       </c>
       <c r="P224" s="1" t="n">
-        <v>46141.57124067251</v>
+        <v>46141.5712406713</v>
+      </c>
+      <c r="Q224" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="225">
@@ -12547,7 +13219,10 @@
         <v>1.80952</v>
       </c>
       <c r="P225" s="1" t="n">
-        <v>46141.57126047999</v>
+        <v>46141.57126047453</v>
+      </c>
+      <c r="Q225" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="226">
@@ -12603,7 +13278,10 @@
         <v>1.22222</v>
       </c>
       <c r="P226" s="1" t="n">
-        <v>46141.57128021759</v>
+        <v>46141.57128021991</v>
+      </c>
+      <c r="Q226" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="227">
@@ -12659,7 +13337,10 @@
         <v>1.875</v>
       </c>
       <c r="P227" s="1" t="n">
-        <v>46141.57130005438</v>
+        <v>46141.57130005787</v>
+      </c>
+      <c r="Q227" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="228">
@@ -12715,7 +13396,10 @@
         <v>1.92308</v>
       </c>
       <c r="P228" s="1" t="n">
-        <v>46141.57131934568</v>
+        <v>46141.57131934028</v>
+      </c>
+      <c r="Q228" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="229">
@@ -12771,7 +13455,10 @@
         <v>1</v>
       </c>
       <c r="P229" s="1" t="n">
-        <v>46141.57133939406</v>
+        <v>46141.57133939815</v>
+      </c>
+      <c r="Q229" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="230">
@@ -12827,7 +13514,10 @@
         <v>2.42857</v>
       </c>
       <c r="P230" s="1" t="n">
-        <v>46141.57135990727</v>
+        <v>46141.57135990741</v>
+      </c>
+      <c r="Q230" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="231">
@@ -12876,10 +13566,11 @@
       <c r="M231" t="n">
         <v>8.003</v>
       </c>
-      <c r="N231" t="inlineStr"/>
-      <c r="O231" t="inlineStr"/>
       <c r="P231" s="1" t="n">
-        <v>46141.57137912622</v>
+        <v>46141.57137913194</v>
+      </c>
+      <c r="Q231" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="232">
@@ -12928,10 +13619,11 @@
       <c r="M232" t="n">
         <v>4.685</v>
       </c>
-      <c r="N232" t="inlineStr"/>
-      <c r="O232" t="inlineStr"/>
       <c r="P232" s="1" t="n">
-        <v>46141.57139685364</v>
+        <v>46141.57139685185</v>
+      </c>
+      <c r="Q232" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="233">
@@ -12980,12 +13672,14 @@
       <c r="M233" t="n">
         <v>32.373</v>
       </c>
-      <c r="N233" t="inlineStr"/>
       <c r="O233" t="n">
         <v>3</v>
       </c>
       <c r="P233" s="1" t="n">
-        <v>46141.57141698483</v>
+        <v>46141.57141697917</v>
+      </c>
+      <c r="Q233" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="234">
@@ -13034,12 +13728,14 @@
       <c r="M234" t="n">
         <v>35.968</v>
       </c>
-      <c r="N234" t="inlineStr"/>
       <c r="O234" t="n">
         <v>2.24</v>
       </c>
       <c r="P234" s="1" t="n">
-        <v>46141.5714363466</v>
+        <v>46141.57143634259</v>
+      </c>
+      <c r="Q234" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="235">
@@ -13076,18 +13772,17 @@
       <c r="I235" t="n">
         <v>1731294336</v>
       </c>
-      <c r="J235" t="inlineStr"/>
       <c r="K235" t="n">
         <v>0</v>
       </c>
       <c r="L235" t="n">
         <v>-0.08400000000000001</v>
       </c>
-      <c r="M235" t="inlineStr"/>
-      <c r="N235" t="inlineStr"/>
-      <c r="O235" t="inlineStr"/>
       <c r="P235" s="1" t="n">
-        <v>46141.57145536936</v>
+        <v>46141.57145537037</v>
+      </c>
+      <c r="Q235" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="236">
@@ -13130,7 +13825,6 @@
       <c r="K236" t="n">
         <v>0.06591000399999999</v>
       </c>
-      <c r="L236" t="inlineStr"/>
       <c r="M236" t="n">
         <v>66.732</v>
       </c>
@@ -13141,7 +13835,10 @@
         <v>1.14286</v>
       </c>
       <c r="P236" s="1" t="n">
-        <v>46141.57147669893</v>
+        <v>46141.57147670139</v>
+      </c>
+      <c r="Q236" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="237">
@@ -13197,7 +13894,10 @@
         <v>2.6</v>
       </c>
       <c r="P237" s="1" t="n">
-        <v>46141.57149663712</v>
+        <v>46141.57149663194</v>
+      </c>
+      <c r="Q237" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="238">
@@ -13255,6 +13955,9 @@
       <c r="P238" s="1" t="n">
         <v>46141.57151673611</v>
       </c>
+      <c r="Q238" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -13309,7 +14012,10 @@
         <v>1.6</v>
       </c>
       <c r="P239" s="1" t="n">
-        <v>46141.57153655272</v>
+        <v>46141.57153655092</v>
+      </c>
+      <c r="Q239" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="240">
@@ -13346,7 +14052,6 @@
       <c r="I240" t="n">
         <v>22799898624</v>
       </c>
-      <c r="J240" t="inlineStr"/>
       <c r="K240" t="n">
         <v>-0.36909</v>
       </c>
@@ -13356,10 +14061,11 @@
       <c r="M240" t="n">
         <v>28.69</v>
       </c>
-      <c r="N240" t="inlineStr"/>
-      <c r="O240" t="inlineStr"/>
       <c r="P240" s="1" t="n">
-        <v>46141.5715562399</v>
+        <v>46141.57155623843</v>
+      </c>
+      <c r="Q240" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="241">
@@ -13411,9 +14117,11 @@
       <c r="N241" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="O241" t="inlineStr"/>
       <c r="P241" s="1" t="n">
-        <v>46141.57157612191</v>
+        <v>46141.57157612268</v>
+      </c>
+      <c r="Q241" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="242">
@@ -13469,7 +14177,10 @@
         <v>2.29412</v>
       </c>
       <c r="P242" s="1" t="n">
-        <v>46141.57159651455</v>
+        <v>46141.5715965162</v>
+      </c>
+      <c r="Q242" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="243">
@@ -13525,7 +14236,10 @@
         <v>1.2381</v>
       </c>
       <c r="P243" s="1" t="n">
-        <v>46141.57161726339</v>
+        <v>46141.57161726852</v>
+      </c>
+      <c r="Q243" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="244">
@@ -13581,7 +14295,10 @@
         <v>1.76471</v>
       </c>
       <c r="P244" s="1" t="n">
-        <v>46141.57164009616</v>
+        <v>46141.5716400926</v>
+      </c>
+      <c r="Q244" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="245">
@@ -13618,7 +14335,6 @@
       <c r="I245" t="n">
         <v>907200064</v>
       </c>
-      <c r="J245" t="inlineStr"/>
       <c r="K245" t="n">
         <v>-0.00557</v>
       </c>
@@ -13631,9 +14347,11 @@
       <c r="N245" t="n">
         <v>5.29</v>
       </c>
-      <c r="O245" t="inlineStr"/>
       <c r="P245" s="1" t="n">
-        <v>46141.57165957744</v>
+        <v>46141.57165957176</v>
+      </c>
+      <c r="Q245" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="246">
@@ -13682,12 +14400,14 @@
       <c r="M246" t="n">
         <v>0.432</v>
       </c>
-      <c r="N246" t="inlineStr"/>
       <c r="O246" t="n">
         <v>2.05556</v>
       </c>
       <c r="P246" s="1" t="n">
-        <v>46141.57168066908</v>
+        <v>46141.5716806713</v>
+      </c>
+      <c r="Q246" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="247">
@@ -13738,10 +14458,11 @@
       <c r="M247" t="n">
         <v>2.089</v>
       </c>
-      <c r="N247" t="inlineStr"/>
-      <c r="O247" t="inlineStr"/>
       <c r="P247" s="1" t="n">
-        <v>46141.57169992077</v>
+        <v>46141.57169991898</v>
+      </c>
+      <c r="Q247" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="248">
@@ -13797,7 +14518,10 @@
         <v>1.29032</v>
       </c>
       <c r="P248" s="1" t="n">
-        <v>46141.57172001377</v>
+        <v>46141.57172001158</v>
+      </c>
+      <c r="Q248" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="249">
@@ -13846,12 +14570,14 @@
       <c r="M249" t="n">
         <v>69.792</v>
       </c>
-      <c r="N249" t="inlineStr"/>
       <c r="O249" t="n">
         <v>1.25</v>
       </c>
       <c r="P249" s="1" t="n">
-        <v>46141.57174763447</v>
+        <v>46141.57174763889</v>
+      </c>
+      <c r="Q249" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="250">
@@ -13902,10 +14628,11 @@
       <c r="M250" t="n">
         <v>350.977</v>
       </c>
-      <c r="N250" t="inlineStr"/>
-      <c r="O250" t="inlineStr"/>
       <c r="P250" s="1" t="n">
-        <v>46141.57177040758</v>
+        <v>46141.57177040509</v>
+      </c>
+      <c r="Q250" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="251">
@@ -13951,7 +14678,6 @@
       <c r="L251" t="n">
         <v>0.035</v>
       </c>
-      <c r="M251" t="inlineStr"/>
       <c r="N251" t="n">
         <v>5.18</v>
       </c>
@@ -13959,7 +14685,10 @@
         <v>1.5</v>
       </c>
       <c r="P251" s="1" t="n">
-        <v>46141.57179066281</v>
+        <v>46141.57179065972</v>
+      </c>
+      <c r="Q251" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="252">
@@ -13996,7 +14725,6 @@
       <c r="I252" t="n">
         <v>35565117440</v>
       </c>
-      <c r="J252" t="inlineStr"/>
       <c r="K252" t="n">
         <v>-0.09795000399999999</v>
       </c>
@@ -14006,12 +14734,14 @@
       <c r="M252" t="n">
         <v>113.286</v>
       </c>
-      <c r="N252" t="inlineStr"/>
       <c r="O252" t="n">
         <v>1.25</v>
       </c>
       <c r="P252" s="1" t="n">
-        <v>46141.57181017692</v>
+        <v>46141.57181017361</v>
+      </c>
+      <c r="Q252" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="253">
@@ -14067,7 +14797,10 @@
         <v>1.47059</v>
       </c>
       <c r="P253" s="1" t="n">
-        <v>46141.57183064496</v>
+        <v>46141.57183064815</v>
+      </c>
+      <c r="Q253" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="254">
@@ -14116,10 +14849,11 @@
       <c r="M254" t="n">
         <v>296.676</v>
       </c>
-      <c r="N254" t="inlineStr"/>
-      <c r="O254" t="inlineStr"/>
       <c r="P254" s="1" t="n">
-        <v>46141.57185038049</v>
+        <v>46141.57185038194</v>
+      </c>
+      <c r="Q254" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="255">
@@ -14175,7 +14909,10 @@
         <v>1.2</v>
       </c>
       <c r="P255" s="1" t="n">
-        <v>46141.57186928771</v>
+        <v>46141.57186928241</v>
+      </c>
+      <c r="Q255" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="256">
@@ -14221,7 +14958,6 @@
       <c r="L256" t="n">
         <v>-0.012</v>
       </c>
-      <c r="M256" t="inlineStr"/>
       <c r="N256" t="n">
         <v>6.6</v>
       </c>
@@ -14229,7 +14965,10 @@
         <v>1.78947</v>
       </c>
       <c r="P256" s="1" t="n">
-        <v>46141.57189025884</v>
+        <v>46141.57189025463</v>
+      </c>
+      <c r="Q256" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="257">
@@ -14266,7 +15005,6 @@
       <c r="I257" t="n">
         <v>14989526016</v>
       </c>
-      <c r="J257" t="inlineStr"/>
       <c r="K257" t="n">
         <v>-0.01909</v>
       </c>
@@ -14276,10 +15014,11 @@
       <c r="M257" t="n">
         <v>240.884</v>
       </c>
-      <c r="N257" t="inlineStr"/>
-      <c r="O257" t="inlineStr"/>
       <c r="P257" s="1" t="n">
-        <v>46141.5719088668</v>
+        <v>46141.57190886574</v>
+      </c>
+      <c r="Q257" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="258">
@@ -14335,7 +15074,10 @@
         <v>1.5</v>
       </c>
       <c r="P258" s="1" t="n">
-        <v>46141.57192823667</v>
+        <v>46141.57192824074</v>
+      </c>
+      <c r="Q258" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="259">
@@ -14387,9 +15129,11 @@
       <c r="N259" t="n">
         <v>0.13</v>
       </c>
-      <c r="O259" t="inlineStr"/>
       <c r="P259" s="1" t="n">
-        <v>46141.57194720117</v>
+        <v>46141.57194719907</v>
+      </c>
+      <c r="Q259" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="260">
@@ -14426,7 +15170,6 @@
       <c r="I260" t="n">
         <v>3424933888</v>
       </c>
-      <c r="J260" t="inlineStr"/>
       <c r="K260" t="n">
         <v>-0.0861</v>
       </c>
@@ -14436,10 +15179,11 @@
       <c r="M260" t="n">
         <v>51.854</v>
       </c>
-      <c r="N260" t="inlineStr"/>
-      <c r="O260" t="inlineStr"/>
       <c r="P260" s="1" t="n">
-        <v>46141.57196687978</v>
+        <v>46141.571966875</v>
+      </c>
+      <c r="Q260" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="261">
@@ -14488,12 +15232,14 @@
       <c r="M261" t="n">
         <v>11.351</v>
       </c>
-      <c r="N261" t="inlineStr"/>
       <c r="O261" t="n">
         <v>1</v>
       </c>
       <c r="P261" s="1" t="n">
-        <v>46141.57198723306</v>
+        <v>46141.57198723379</v>
+      </c>
+      <c r="Q261" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="262">
@@ -14530,7 +15276,6 @@
       <c r="I262" t="n">
         <v>513399980032</v>
       </c>
-      <c r="J262" t="inlineStr"/>
       <c r="K262" t="n">
         <v>-0.06401</v>
       </c>
@@ -14540,12 +15285,14 @@
       <c r="M262" t="n">
         <v>57.368</v>
       </c>
-      <c r="N262" t="inlineStr"/>
       <c r="O262" t="n">
         <v>1.86842</v>
       </c>
       <c r="P262" s="1" t="n">
-        <v>46141.57200678594</v>
+        <v>46141.57200678241</v>
+      </c>
+      <c r="Q262" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="263">
@@ -14582,7 +15329,6 @@
       <c r="I263" t="n">
         <v>39179988992</v>
       </c>
-      <c r="J263" t="inlineStr"/>
       <c r="K263" t="n">
         <v>-0.01881</v>
       </c>
@@ -14599,7 +15345,10 @@
         <v>1.2</v>
       </c>
       <c r="P263" s="1" t="n">
-        <v>46141.57202789329</v>
+        <v>46141.57202789352</v>
+      </c>
+      <c r="Q263" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="264">
@@ -14655,7 +15404,10 @@
         <v>1</v>
       </c>
       <c r="P264" s="1" t="n">
-        <v>46141.57204844991</v>
+        <v>46141.57204844907</v>
+      </c>
+      <c r="Q264" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="265">
@@ -14704,10 +15456,11 @@
       <c r="M265" t="n">
         <v>33.656</v>
       </c>
-      <c r="N265" t="inlineStr"/>
-      <c r="O265" t="inlineStr"/>
       <c r="P265" s="1" t="n">
-        <v>46141.57206814778</v>
+        <v>46141.57206814815</v>
+      </c>
+      <c r="Q265" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="266">
@@ -14753,7 +15506,6 @@
       <c r="L266" t="n">
         <v>-0.043</v>
       </c>
-      <c r="M266" t="inlineStr"/>
       <c r="N266" t="n">
         <v>4.97</v>
       </c>
@@ -14761,7 +15513,10 @@
         <v>2.17647</v>
       </c>
       <c r="P266" s="1" t="n">
-        <v>46141.57209039827</v>
+        <v>46141.57209039352</v>
+      </c>
+      <c r="Q266" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="267">
@@ -14813,9 +15568,11 @@
       <c r="N267" t="n">
         <v>3.71</v>
       </c>
-      <c r="O267" t="inlineStr"/>
       <c r="P267" s="1" t="n">
-        <v>46141.57211237807</v>
+        <v>46141.57211237268</v>
+      </c>
+      <c r="Q267" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="268">
@@ -14852,7 +15609,6 @@
       <c r="I268" t="n">
         <v>36269355008</v>
       </c>
-      <c r="J268" t="inlineStr"/>
       <c r="K268" t="n">
         <v>-0.37937</v>
       </c>
@@ -14862,12 +15618,14 @@
       <c r="M268" t="n">
         <v>159.586</v>
       </c>
-      <c r="N268" t="inlineStr"/>
       <c r="O268" t="n">
         <v>4</v>
       </c>
       <c r="P268" s="1" t="n">
-        <v>46141.57213361677</v>
+        <v>46141.57213361111</v>
+      </c>
+      <c r="Q268" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="269">
@@ -14923,7 +15681,10 @@
         <v>1.34286</v>
       </c>
       <c r="P269" s="1" t="n">
-        <v>46141.57215433219</v>
+        <v>46141.57215432871</v>
+      </c>
+      <c r="Q269" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="270">
@@ -14972,12 +15733,14 @@
       <c r="M270" t="n">
         <v>41.513</v>
       </c>
-      <c r="N270" t="inlineStr"/>
       <c r="O270" t="n">
         <v>2.13043</v>
       </c>
       <c r="P270" s="1" t="n">
-        <v>46141.57217605731</v>
+        <v>46141.57217605324</v>
+      </c>
+      <c r="Q270" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="271">
@@ -15029,9 +15792,11 @@
       <c r="N271" t="n">
         <v>2.4</v>
       </c>
-      <c r="O271" t="inlineStr"/>
       <c r="P271" s="1" t="n">
-        <v>46141.57219687568</v>
+        <v>46141.572196875</v>
+      </c>
+      <c r="Q271" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="272">
@@ -15087,7 +15852,10 @@
         <v>1.2</v>
       </c>
       <c r="P272" s="1" t="n">
-        <v>46141.57221829758</v>
+        <v>46141.57221829861</v>
+      </c>
+      <c r="Q272" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="273">
@@ -15139,9 +15907,11 @@
       <c r="N273" t="n">
         <v>1.41</v>
       </c>
-      <c r="O273" t="inlineStr"/>
       <c r="P273" s="1" t="n">
-        <v>46141.57223996605</v>
+        <v>46141.57223996528</v>
+      </c>
+      <c r="Q273" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="274">
@@ -15190,12 +15960,14 @@
       <c r="M274" t="n">
         <v>0.507</v>
       </c>
-      <c r="N274" t="inlineStr"/>
       <c r="O274" t="n">
         <v>1.5</v>
       </c>
       <c r="P274" s="1" t="n">
-        <v>46141.57226183025</v>
+        <v>46141.5722618287</v>
+      </c>
+      <c r="Q274" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="275">
@@ -15251,7 +16023,10 @@
         <v>1.38462</v>
       </c>
       <c r="P275" s="1" t="n">
-        <v>46141.57228327389</v>
+        <v>46141.57228327546</v>
+      </c>
+      <c r="Q275" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="276">
@@ -15288,7 +16063,6 @@
       <c r="I276" t="n">
         <v>2693616128</v>
       </c>
-      <c r="J276" t="inlineStr"/>
       <c r="K276" t="n">
         <v>-0.49305</v>
       </c>
@@ -15298,10 +16072,11 @@
       <c r="M276" t="n">
         <v>287.717</v>
       </c>
-      <c r="N276" t="inlineStr"/>
-      <c r="O276" t="inlineStr"/>
       <c r="P276" s="1" t="n">
-        <v>46141.57230625557</v>
+        <v>46141.57230625</v>
+      </c>
+      <c r="Q276" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="277">
@@ -15347,7 +16122,6 @@
       <c r="L277" t="n">
         <v>0.028</v>
       </c>
-      <c r="M277" t="inlineStr"/>
       <c r="N277" t="n">
         <v>4.69</v>
       </c>
@@ -15355,7 +16129,10 @@
         <v>1.875</v>
       </c>
       <c r="P277" s="1" t="n">
-        <v>46141.57232727673</v>
+        <v>46141.57232728009</v>
+      </c>
+      <c r="Q277" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="278">
@@ -15404,10 +16181,11 @@
       <c r="M278" t="n">
         <v>6.324</v>
       </c>
-      <c r="N278" t="inlineStr"/>
-      <c r="O278" t="inlineStr"/>
       <c r="P278" s="1" t="n">
-        <v>46141.57234965356</v>
+        <v>46141.57234965278</v>
+      </c>
+      <c r="Q278" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="279">
@@ -15456,10 +16234,11 @@
       <c r="M279" t="n">
         <v>325.218</v>
       </c>
-      <c r="N279" t="inlineStr"/>
-      <c r="O279" t="inlineStr"/>
       <c r="P279" s="1" t="n">
-        <v>46141.57237118988</v>
+        <v>46141.57237119213</v>
+      </c>
+      <c r="Q279" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="280">
@@ -15502,7 +16281,6 @@
       <c r="K280" t="n">
         <v>0.15106</v>
       </c>
-      <c r="L280" t="inlineStr"/>
       <c r="M280" t="n">
         <v>29.176</v>
       </c>
@@ -15513,7 +16291,10 @@
         <v>1.18182</v>
       </c>
       <c r="P280" s="1" t="n">
-        <v>46141.57239068532</v>
+        <v>46141.57239068287</v>
+      </c>
+      <c r="Q280" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="281">
@@ -15550,7 +16331,6 @@
       <c r="I281" t="n">
         <v>4967095808</v>
       </c>
-      <c r="J281" t="inlineStr"/>
       <c r="K281" t="n">
         <v>-1.18725</v>
       </c>
@@ -15560,10 +16340,11 @@
       <c r="M281" t="n">
         <v>32.949</v>
       </c>
-      <c r="N281" t="inlineStr"/>
-      <c r="O281" t="inlineStr"/>
       <c r="P281" s="1" t="n">
-        <v>46141.57241100494</v>
+        <v>46141.57241100694</v>
+      </c>
+      <c r="Q281" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="282">
@@ -15615,9 +16396,11 @@
       <c r="N282" t="n">
         <v>2.7</v>
       </c>
-      <c r="O282" t="inlineStr"/>
       <c r="P282" s="1" t="n">
-        <v>46141.57243199299</v>
+        <v>46141.57243199074</v>
+      </c>
+      <c r="Q282" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="283">
@@ -15654,7 +16437,6 @@
       <c r="I283" t="n">
         <v>30285285376</v>
       </c>
-      <c r="J283" t="inlineStr"/>
       <c r="K283" t="n">
         <v>-0.09097999</v>
       </c>
@@ -15671,7 +16453,10 @@
         <v>2.86667</v>
       </c>
       <c r="P283" s="1" t="n">
-        <v>46141.57245126754</v>
+        <v>46141.57245127315</v>
+      </c>
+      <c r="Q283" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="284">
@@ -15720,10 +16505,11 @@
       <c r="M284" t="n">
         <v>307.316</v>
       </c>
-      <c r="N284" t="inlineStr"/>
-      <c r="O284" t="inlineStr"/>
       <c r="P284" s="1" t="n">
-        <v>46141.57247102588</v>
+        <v>46141.57247103009</v>
+      </c>
+      <c r="Q284" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="285">
@@ -15772,10 +16558,11 @@
       <c r="M285" t="n">
         <v>0.231</v>
       </c>
-      <c r="N285" t="inlineStr"/>
-      <c r="O285" t="inlineStr"/>
       <c r="P285" s="1" t="n">
-        <v>46141.57249110543</v>
+        <v>46141.57249111111</v>
+      </c>
+      <c r="Q285" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="286">
@@ -15831,7 +16618,10 @@
         <v>1.6875</v>
       </c>
       <c r="P286" s="1" t="n">
-        <v>46141.57251157112</v>
+        <v>46141.57251157407</v>
+      </c>
+      <c r="Q286" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="287">
@@ -15887,7 +16677,10 @@
         <v>2.15385</v>
       </c>
       <c r="P287" s="1" t="n">
-        <v>46141.57253115584</v>
+        <v>46141.57253115741</v>
+      </c>
+      <c r="Q287" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="288">
@@ -15943,7 +16736,10 @@
         <v>1.28571</v>
       </c>
       <c r="P288" s="1" t="n">
-        <v>46141.57255040439</v>
+        <v>46141.57255040509</v>
+      </c>
+      <c r="Q288" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="289">
@@ -15986,14 +16782,14 @@
       <c r="K289" t="n">
         <v>1.98584</v>
       </c>
-      <c r="L289" t="inlineStr"/>
       <c r="M289" t="n">
         <v>1816.918</v>
       </c>
-      <c r="N289" t="inlineStr"/>
-      <c r="O289" t="inlineStr"/>
       <c r="P289" s="1" t="n">
-        <v>46141.57257072557</v>
+        <v>46141.57257072916</v>
+      </c>
+      <c r="Q289" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="290">
@@ -16045,9 +16841,11 @@
       <c r="N290" t="n">
         <v>1.63</v>
       </c>
-      <c r="O290" t="inlineStr"/>
       <c r="P290" s="1" t="n">
-        <v>46141.5725897145</v>
+        <v>46141.57258971065</v>
+      </c>
+      <c r="Q290" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="291">
@@ -16084,7 +16882,6 @@
       <c r="I291" t="n">
         <v>83054493696</v>
       </c>
-      <c r="J291" t="inlineStr"/>
       <c r="K291" t="n">
         <v>-0.010319999</v>
       </c>
@@ -16094,12 +16891,14 @@
       <c r="M291" t="n">
         <v>575.043</v>
       </c>
-      <c r="N291" t="inlineStr"/>
       <c r="O291" t="n">
         <v>2.88889</v>
       </c>
       <c r="P291" s="1" t="n">
-        <v>46141.57260924338</v>
+        <v>46141.57260924768</v>
+      </c>
+      <c r="Q291" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="292">
@@ -16151,9 +16950,11 @@
       <c r="N292" t="n">
         <v>5.09</v>
       </c>
-      <c r="O292" t="inlineStr"/>
       <c r="P292" s="1" t="n">
-        <v>46141.57262974213</v>
+        <v>46141.57262974537</v>
+      </c>
+      <c r="Q292" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="293">
@@ -16190,16 +16991,14 @@
       <c r="I293" t="n">
         <v>648375808</v>
       </c>
-      <c r="J293" t="inlineStr"/>
       <c r="K293" t="n">
         <v>0</v>
       </c>
-      <c r="L293" t="inlineStr"/>
-      <c r="M293" t="inlineStr"/>
-      <c r="N293" t="inlineStr"/>
-      <c r="O293" t="inlineStr"/>
       <c r="P293" s="1" t="n">
-        <v>46141.57264912457</v>
+        <v>46141.57264912037</v>
+      </c>
+      <c r="Q293" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="294">
@@ -16248,12 +17047,14 @@
       <c r="M294" t="n">
         <v>5.852</v>
       </c>
-      <c r="N294" t="inlineStr"/>
       <c r="O294" t="n">
         <v>1.52</v>
       </c>
       <c r="P294" s="1" t="n">
-        <v>46141.57266938348</v>
+        <v>46141.57266938657</v>
+      </c>
+      <c r="Q294" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="295">
@@ -16302,10 +17103,11 @@
       <c r="M295" t="n">
         <v>238.6</v>
       </c>
-      <c r="N295" t="inlineStr"/>
-      <c r="O295" t="inlineStr"/>
       <c r="P295" s="1" t="n">
-        <v>46141.57270041499</v>
+        <v>46141.57270041667</v>
+      </c>
+      <c r="Q295" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="296">
@@ -16342,7 +17144,6 @@
       <c r="I296" t="n">
         <v>2400000000</v>
       </c>
-      <c r="J296" t="inlineStr"/>
       <c r="K296" t="n">
         <v>-0.28458</v>
       </c>
@@ -16352,10 +17153,11 @@
       <c r="M296" t="n">
         <v>0.528</v>
       </c>
-      <c r="N296" t="inlineStr"/>
-      <c r="O296" t="inlineStr"/>
       <c r="P296" s="1" t="n">
-        <v>46141.57272047354</v>
+        <v>46141.57272047453</v>
+      </c>
+      <c r="Q296" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="297">
@@ -16411,7 +17213,10 @@
         <v>1.36842</v>
       </c>
       <c r="P297" s="1" t="n">
-        <v>46141.57274050584</v>
+        <v>46141.57274050926</v>
+      </c>
+      <c r="Q297" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="298">
@@ -16463,9 +17268,11 @@
       <c r="N298" t="n">
         <v>4.24</v>
       </c>
-      <c r="O298" t="inlineStr"/>
       <c r="P298" s="1" t="n">
-        <v>46141.57276141965</v>
+        <v>46141.57276142361</v>
+      </c>
+      <c r="Q298" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="299">
@@ -16517,9 +17324,11 @@
       <c r="N299" t="n">
         <v>1.59</v>
       </c>
-      <c r="O299" t="inlineStr"/>
       <c r="P299" s="1" t="n">
-        <v>46141.57278190179</v>
+        <v>46141.57278189815</v>
+      </c>
+      <c r="Q299" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="300">
@@ -16571,9 +17380,11 @@
       <c r="N300" t="n">
         <v>4.64</v>
       </c>
-      <c r="O300" t="inlineStr"/>
       <c r="P300" s="1" t="n">
-        <v>46141.57280145243</v>
+        <v>46141.57280144676</v>
+      </c>
+      <c r="Q300" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="301">
@@ -16629,10 +17440,13 @@
         <v>1.42857</v>
       </c>
       <c r="P301" s="1" t="n">
-        <v>46141.57282261908</v>
+        <v>46141.57282261574</v>
+      </c>
+      <c r="Q301" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>